--- a/AAII_Financials/Quarterly/VYX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VYX_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -302,7 +302,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -344,7 +344,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -713,7 +713,7 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>2017000</v>
+        <v>2867000</v>
       </c>
       <c r="E8" s="3">
         <v>1986000</v>
@@ -742,7 +742,7 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>1390000</v>
+        <v>3476000</v>
       </c>
       <c r="E9" s="3">
         <v>1448000</v>
@@ -771,7 +771,7 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>627000</v>
+        <v>-609000</v>
       </c>
       <c r="E10" s="3">
         <v>538000</v>
@@ -813,7 +813,7 @@
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>54000</v>
+        <v>183000</v>
       </c>
       <c r="E12" s="3">
         <v>57000</v>
@@ -939,7 +939,7 @@
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>1775000</v>
+        <v>2700000</v>
       </c>
       <c r="E17" s="3">
         <v>1838000</v>
@@ -968,7 +968,7 @@
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>242000</v>
+        <v>167000</v>
       </c>
       <c r="E18" s="3">
         <v>148000</v>
@@ -1010,7 +1010,7 @@
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>-44000</v>
+        <v>-38000</v>
       </c>
       <c r="E20" s="3">
         <v>-8000</v>
@@ -1039,7 +1039,7 @@
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>353000</v>
+        <v>590000</v>
       </c>
       <c r="E21" s="3">
         <v>295000</v>
@@ -1068,7 +1068,7 @@
         <v>16</v>
       </c>
       <c r="D22" s="3">
-        <v>85000</v>
+        <v>257000</v>
       </c>
       <c r="E22" s="3">
         <v>91000</v>
@@ -1097,7 +1097,7 @@
         <v>17</v>
       </c>
       <c r="D23" s="3">
-        <v>113000</v>
+        <v>-128000</v>
       </c>
       <c r="E23" s="3">
         <v>49000</v>
@@ -1126,7 +1126,7 @@
         <v>18</v>
       </c>
       <c r="D24" s="3">
-        <v>236000</v>
+        <v>202000</v>
       </c>
       <c r="E24" s="3">
         <v>30000</v>
@@ -1184,7 +1184,7 @@
         <v>20</v>
       </c>
       <c r="D26" s="3">
-        <v>-123000</v>
+        <v>-330000</v>
       </c>
       <c r="E26" s="3">
         <v>19000</v>
@@ -1213,7 +1213,7 @@
         <v>21</v>
       </c>
       <c r="D27" s="3">
-        <v>-128000</v>
+        <v>-343000</v>
       </c>
       <c r="E27" s="3">
         <v>16000</v>
@@ -1271,7 +1271,7 @@
         <v>23</v>
       </c>
       <c r="D29" s="3">
-        <v>0</v>
+        <v>223000</v>
       </c>
       <c r="E29" s="3">
         <v>-1000</v>
@@ -1358,7 +1358,7 @@
         <v>26</v>
       </c>
       <c r="D32" s="3">
-        <v>44000</v>
+        <v>38000</v>
       </c>
       <c r="E32" s="3">
         <v>8000</v>
@@ -1387,7 +1387,7 @@
         <v>27</v>
       </c>
       <c r="D33" s="3">
-        <v>-128000</v>
+        <v>-120000</v>
       </c>
       <c r="E33" s="3">
         <v>15000</v>
@@ -1445,7 +1445,7 @@
         <v>29</v>
       </c>
       <c r="D35" s="3">
-        <v>-128000</v>
+        <v>-120000</v>
       </c>
       <c r="E35" s="3">
         <v>15000</v>
@@ -2593,7 +2593,7 @@
         <v>27</v>
       </c>
       <c r="D81" s="3">
-        <v>-128000</v>
+        <v>-120000</v>
       </c>
       <c r="E81" s="3">
         <v>15000</v>
@@ -2635,7 +2635,7 @@
         <v>71</v>
       </c>
       <c r="D83" s="3">
-        <v>155000</v>
+        <v>461000</v>
       </c>
       <c r="E83" s="3">
         <v>155000</v>
@@ -2809,7 +2809,7 @@
         <v>77</v>
       </c>
       <c r="D89" s="3">
-        <v>189000</v>
+        <v>727000</v>
       </c>
       <c r="E89" s="3">
         <v>227000</v>
@@ -2938,7 +2938,7 @@
         <v>82</v>
       </c>
       <c r="D94" s="3">
-        <v>-111000</v>
+        <v>-305000</v>
       </c>
       <c r="E94" s="3">
         <v>-108000</v>
@@ -3096,7 +3096,7 @@
         <v>88</v>
       </c>
       <c r="D100" s="3">
-        <v>2145000</v>
+        <v>1879000</v>
       </c>
       <c r="E100" s="3">
         <v>-91000</v>
@@ -3125,7 +3125,7 @@
         <v>89</v>
       </c>
       <c r="D101" s="3">
-        <v>-20000</v>
+        <v>-28000</v>
       </c>
       <c r="E101" s="3">
         <v>2000</v>
@@ -3154,7 +3154,7 @@
         <v>90</v>
       </c>
       <c r="D102" s="3">
-        <v>2203000</v>
+        <v>2273000</v>
       </c>
       <c r="E102" s="3">
         <v>30000</v>

--- a/AAII_Financials/Quarterly/VYX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VYX_QTR_FIN.xlsx
@@ -653,149 +653,174 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:K102"/>
+  <dimension ref="A5:M102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>2867000</v>
+        <v>862000</v>
       </c>
       <c r="E8" s="3">
+        <v>3830000</v>
+      </c>
+      <c r="F8" s="3">
+        <v>2017000</v>
+      </c>
+      <c r="G8" s="3">
         <v>1986000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>1891000</v>
       </c>
-      <c r="G8" s="3">
-        <v>2009000</v>
-      </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
+        <v>3793000</v>
+      </c>
+      <c r="J8" s="3">
         <v>1972000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>1997000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>1866000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>2034000</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>3476000</v>
+        <v>666000</v>
       </c>
       <c r="E9" s="3">
+        <v>2868000</v>
+      </c>
+      <c r="F9" s="3">
+        <v>1390000</v>
+      </c>
+      <c r="G9" s="3">
         <v>1448000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>1425000</v>
       </c>
-      <c r="G9" s="3">
-        <v>1524000</v>
-      </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
+        <v>2815000</v>
+      </c>
+      <c r="J9" s="3">
         <v>1481000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>1526000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>1455000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>1531000</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>-609000</v>
+        <v>196000</v>
       </c>
       <c r="E10" s="3">
+        <v>962000</v>
+      </c>
+      <c r="F10" s="3">
+        <v>627000</v>
+      </c>
+      <c r="G10" s="3">
         <v>538000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>466000</v>
       </c>
-      <c r="G10" s="3">
-        <v>485000</v>
-      </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
+        <v>978000</v>
+      </c>
+      <c r="J10" s="3">
         <v>491000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>471000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>411000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>503000</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -807,37 +832,45 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L11" s="3"/>
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>183000</v>
+        <v>56000</v>
       </c>
       <c r="E12" s="3">
+        <v>185000</v>
+      </c>
+      <c r="F12" s="3">
+        <v>54000</v>
+      </c>
+      <c r="G12" s="3">
         <v>57000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>64000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
+        <v>127000</v>
+      </c>
+      <c r="J12" s="3">
+        <v>39000</v>
+      </c>
+      <c r="K12" s="3">
         <v>51000</v>
       </c>
-      <c r="H12" s="3">
-        <v>39000</v>
-      </c>
-      <c r="I12" s="3">
-        <v>51000</v>
-      </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>64000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>63000</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -865,66 +898,84 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>23000</v>
+      </c>
+      <c r="E14" s="3">
+        <v>128000</v>
+      </c>
+      <c r="F14" s="3">
         <v>72000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>57000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="H14" s="3">
         <v>22000</v>
       </c>
-      <c r="G14" s="3">
-        <v>13000</v>
-      </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
+        <v>62000</v>
+      </c>
+      <c r="J14" s="3">
         <v>9000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="K14" s="3">
         <v>35000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="L14" s="3">
         <v>31000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="M14" s="3">
         <v>23000</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>16000</v>
+        <v>10000</v>
       </c>
       <c r="E15" s="3">
-        <v>16000</v>
+        <v>33000</v>
       </c>
       <c r="F15" s="3">
         <v>16000</v>
       </c>
       <c r="G15" s="3">
-        <v>15000</v>
+        <v>16000</v>
       </c>
       <c r="H15" s="3">
+        <v>16000</v>
+      </c>
+      <c r="I15" s="3">
+        <v>30000</v>
+      </c>
+      <c r="J15" s="3">
         <v>17000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>18000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>22000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>23000</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -933,66 +984,80 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L16" s="3"/>
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>2700000</v>
+        <v>858000</v>
       </c>
       <c r="E17" s="3">
+        <v>3839000</v>
+      </c>
+      <c r="F17" s="3">
+        <v>1775000</v>
+      </c>
+      <c r="G17" s="3">
         <v>1838000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>1781000</v>
       </c>
-      <c r="G17" s="3">
-        <v>1843000</v>
-      </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
+        <v>3657000</v>
+      </c>
+      <c r="J17" s="3">
         <v>1785000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>1894000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>1833000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>1911000</v>
       </c>
     </row>
-    <row r="18" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>167000</v>
+        <v>4000</v>
       </c>
       <c r="E18" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="F18" s="3">
+        <v>242000</v>
+      </c>
+      <c r="G18" s="3">
         <v>148000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>110000</v>
       </c>
-      <c r="G18" s="3">
-        <v>166000</v>
-      </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
+        <v>136000</v>
+      </c>
+      <c r="J18" s="3">
         <v>187000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>103000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>33000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>123000</v>
       </c>
     </row>
-    <row r="19" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1004,153 +1069,185 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L19" s="3"/>
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>-38000</v>
+        <v>-20000</v>
       </c>
       <c r="E20" s="3">
+        <v>-79000</v>
+      </c>
+      <c r="F20" s="3">
+        <v>-44000</v>
+      </c>
+      <c r="G20" s="3">
         <v>-8000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>-3000</v>
       </c>
-      <c r="G20" s="3">
-        <v>-2000</v>
-      </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
+        <v>99000</v>
+      </c>
+      <c r="J20" s="3">
         <v>-1000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>1000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>9000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>113000</v>
       </c>
     </row>
-    <row r="21" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>590000</v>
+        <v>65000</v>
       </c>
       <c r="E21" s="3">
+        <v>471000</v>
+      </c>
+      <c r="F21" s="3">
+        <v>353000</v>
+      </c>
+      <c r="G21" s="3">
         <v>295000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>258000</v>
       </c>
-      <c r="G21" s="3">
-        <v>323000</v>
-      </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
+        <v>845000</v>
+      </c>
+      <c r="J21" s="3">
         <v>338000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>256000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>189000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>389000</v>
       </c>
     </row>
-    <row r="22" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
-        <v>257000</v>
+        <v>39000</v>
       </c>
       <c r="E22" s="3">
+        <v>294000</v>
+      </c>
+      <c r="F22" s="3">
+        <v>85000</v>
+      </c>
+      <c r="G22" s="3">
         <v>91000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>83000</v>
       </c>
-      <c r="G22" s="3">
-        <v>81000</v>
-      </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
+        <v>366000</v>
+      </c>
+      <c r="J22" s="3">
         <v>74000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>67000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>63000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>64000</v>
       </c>
     </row>
-    <row r="23" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
-        <v>-128000</v>
+        <v>-55000</v>
       </c>
       <c r="E23" s="3">
+        <v>-382000</v>
+      </c>
+      <c r="F23" s="3">
+        <v>113000</v>
+      </c>
+      <c r="G23" s="3">
         <v>49000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>24000</v>
       </c>
-      <c r="G23" s="3">
-        <v>83000</v>
-      </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
+        <v>-131000</v>
+      </c>
+      <c r="J23" s="3">
         <v>112000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>37000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-21000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>172000</v>
       </c>
     </row>
-    <row r="24" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
-        <v>202000</v>
+        <v>-14000</v>
       </c>
       <c r="E24" s="3">
+        <v>204000</v>
+      </c>
+      <c r="F24" s="3">
+        <v>236000</v>
+      </c>
+      <c r="G24" s="3">
         <v>30000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>14000</v>
       </c>
-      <c r="G24" s="3">
-        <v>92000</v>
-      </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
+        <v>72000</v>
+      </c>
+      <c r="J24" s="3">
         <v>43000</v>
       </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3">
         <v>13000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>109000</v>
       </c>
     </row>
-    <row r="25" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1178,66 +1275,84 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
-        <v>-330000</v>
+        <v>-41000</v>
       </c>
       <c r="E26" s="3">
+        <v>-586000</v>
+      </c>
+      <c r="F26" s="3">
+        <v>-123000</v>
+      </c>
+      <c r="G26" s="3">
         <v>19000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>10000</v>
       </c>
-      <c r="G26" s="3">
-        <v>-9000</v>
-      </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
+        <v>-203000</v>
+      </c>
+      <c r="J26" s="3">
         <v>69000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>37000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-34000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>63000</v>
       </c>
     </row>
-    <row r="27" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
-        <v>-343000</v>
+        <v>-44000</v>
       </c>
       <c r="E27" s="3">
+        <v>-602000</v>
+      </c>
+      <c r="F27" s="3">
+        <v>-128000</v>
+      </c>
+      <c r="G27" s="3">
         <v>16000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>5000</v>
       </c>
-      <c r="G27" s="3">
-        <v>-11000</v>
-      </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
+        <v>-217000</v>
+      </c>
+      <c r="J27" s="3">
         <v>65000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>31000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-37000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>60000</v>
       </c>
     </row>
-    <row r="28" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -1265,37 +1380,49 @@
       <c r="K28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D29" s="3">
-        <v>223000</v>
+        <v>0</v>
       </c>
       <c r="E29" s="3">
+        <v>163000</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
         <v>-1000</v>
       </c>
-      <c r="F29" s="3">
-        <v>0</v>
-      </c>
-      <c r="G29" s="3">
-        <v>-9000</v>
-      </c>
       <c r="H29" s="3">
         <v>0</v>
       </c>
       <c r="I29" s="3">
+        <v>263000</v>
+      </c>
+      <c r="J29" s="3">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3">
         <v>6000</v>
       </c>
-      <c r="J29" s="3">
+      <c r="L29" s="3">
         <v>-1000</v>
       </c>
-      <c r="K29" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -1323,8 +1450,14 @@
       <c r="K30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -1352,66 +1485,84 @@
       <c r="K31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
-        <v>38000</v>
+        <v>20000</v>
       </c>
       <c r="E32" s="3">
+        <v>79000</v>
+      </c>
+      <c r="F32" s="3">
+        <v>44000</v>
+      </c>
+      <c r="G32" s="3">
         <v>8000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>3000</v>
       </c>
-      <c r="G32" s="3">
-        <v>2000</v>
-      </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
+        <v>-99000</v>
+      </c>
+      <c r="J32" s="3">
         <v>1000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>-1000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-9000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-113000</v>
       </c>
     </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
-        <v>-120000</v>
+        <v>-44000</v>
       </c>
       <c r="E33" s="3">
+        <v>-439000</v>
+      </c>
+      <c r="F33" s="3">
+        <v>-128000</v>
+      </c>
+      <c r="G33" s="3">
         <v>15000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>5000</v>
       </c>
-      <c r="G33" s="3">
-        <v>-20000</v>
-      </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
+        <v>46000</v>
+      </c>
+      <c r="J33" s="3">
         <v>65000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>37000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-38000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>60000</v>
       </c>
     </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -1439,71 +1590,89 @@
       <c r="K34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
-        <v>-120000</v>
+        <v>-44000</v>
       </c>
       <c r="E35" s="3">
+        <v>-439000</v>
+      </c>
+      <c r="F35" s="3">
+        <v>-128000</v>
+      </c>
+      <c r="G35" s="3">
         <v>15000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>5000</v>
       </c>
-      <c r="G35" s="3">
-        <v>-20000</v>
-      </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
+        <v>46000</v>
+      </c>
+      <c r="J35" s="3">
         <v>65000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>37000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-38000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>60000</v>
       </c>
     </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
     </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -1515,8 +1684,10 @@
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L39" s="3"/>
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -1528,37 +1699,45 @@
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L40" s="3"/>
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>246000</v>
+      </c>
+      <c r="E41" s="3">
+        <v>262000</v>
+      </c>
+      <c r="F41" s="3">
         <v>675000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>547000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>519000</v>
       </c>
-      <c r="G41" s="3">
-        <v>505000</v>
-      </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
+        <v>221000</v>
+      </c>
+      <c r="J41" s="3">
         <v>434000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>398000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>412000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>447000</v>
       </c>
     </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
@@ -1586,124 +1765,154 @@
       <c r="K42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
+        <v>484000</v>
+      </c>
+      <c r="E43" s="3">
+        <v>481000</v>
+      </c>
+      <c r="F43" s="3">
         <v>950000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>986000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>1009000</v>
       </c>
-      <c r="G43" s="3">
-        <v>1083000</v>
-      </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
+        <v>550000</v>
+      </c>
+      <c r="J43" s="3">
         <v>1116000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>1085000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>1071000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>959000</v>
       </c>
     </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
+        <v>259000</v>
+      </c>
+      <c r="E44" s="3">
+        <v>254000</v>
+      </c>
+      <c r="F44" s="3">
         <v>725000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>709000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>792000</v>
       </c>
-      <c r="G44" s="3">
-        <v>772000</v>
-      </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
+        <v>357000</v>
+      </c>
+      <c r="J44" s="3">
         <v>827000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>858000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>805000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>754000</v>
       </c>
     </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3">
+        <v>249000</v>
+      </c>
+      <c r="E45" s="3">
+        <v>209000</v>
+      </c>
+      <c r="F45" s="3">
         <v>743000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>712000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>750000</v>
       </c>
-      <c r="G45" s="3">
-        <v>722000</v>
-      </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
+        <v>1954000</v>
+      </c>
+      <c r="J45" s="3">
         <v>814000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>713000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>688000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>716000</v>
       </c>
     </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
+        <v>1238000</v>
+      </c>
+      <c r="E46" s="3">
+        <v>1206000</v>
+      </c>
+      <c r="F46" s="3">
         <v>3093000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>2954000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>3070000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>3082000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>3191000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>3054000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>2976000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>2876000</v>
       </c>
     </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
@@ -1731,66 +1940,84 @@
       <c r="K47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L47" s="3">
+        <v>0</v>
+      </c>
+      <c r="M47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
+        <v>448000</v>
+      </c>
+      <c r="E48" s="3">
+        <v>448000</v>
+      </c>
+      <c r="F48" s="3">
         <v>1029000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>1030000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>1034000</v>
       </c>
-      <c r="G48" s="3">
-        <v>1034000</v>
-      </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
+        <v>499000</v>
+      </c>
+      <c r="J48" s="3">
         <v>997000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>1039000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>1075000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>1122000</v>
       </c>
     </row>
-    <row r="49" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
+        <v>2316000</v>
+      </c>
+      <c r="E49" s="3">
+        <v>2331000</v>
+      </c>
+      <c r="F49" s="3">
         <v>5547000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>5608000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>5647000</v>
       </c>
-      <c r="G49" s="3">
-        <v>5685000</v>
-      </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
+        <v>2480000</v>
+      </c>
+      <c r="J49" s="3">
         <v>5756000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>5825000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>5879000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>5835000</v>
       </c>
     </row>
-    <row r="50" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -1818,8 +2045,14 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -1847,37 +2080,49 @@
       <c r="K51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
+        <v>1005000</v>
+      </c>
+      <c r="E52" s="3">
+        <v>1005000</v>
+      </c>
+      <c r="F52" s="3">
         <v>3554000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>1687000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>1691000</v>
       </c>
-      <c r="G52" s="3">
-        <v>1706000</v>
-      </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
+        <v>6342000</v>
+      </c>
+      <c r="J52" s="3">
         <v>1839000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>1838000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>1785000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>1808000</v>
       </c>
     </row>
-    <row r="53" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -1905,37 +2150,49 @@
       <c r="K53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
+        <v>5007000</v>
+      </c>
+      <c r="E54" s="3">
+        <v>4990000</v>
+      </c>
+      <c r="F54" s="3">
         <v>13223000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>11279000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>11442000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>11507000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>11783000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>11756000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>11715000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>11641000</v>
       </c>
     </row>
-    <row r="55" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -1947,8 +2204,10 @@
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
-    </row>
-    <row r="56" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L55" s="3"/>
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -1960,182 +2219,220 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
-    </row>
-    <row r="57" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L56" s="3"/>
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
+        <v>482000</v>
+      </c>
+      <c r="E57" s="3">
+        <v>505000</v>
+      </c>
+      <c r="F57" s="3">
         <v>820000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>832000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>952000</v>
       </c>
-      <c r="G57" s="3">
-        <v>942000</v>
-      </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
+        <v>594000</v>
+      </c>
+      <c r="J57" s="3">
         <v>876000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>949000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>901000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>826000</v>
       </c>
     </row>
-    <row r="58" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
+        <v>15000</v>
+      </c>
+      <c r="E58" s="3">
+        <v>23000</v>
+      </c>
+      <c r="F58" s="3">
         <v>113000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>105000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>105000</v>
       </c>
-      <c r="G58" s="3">
-        <v>104000</v>
-      </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
+        <v>110000</v>
+      </c>
+      <c r="J58" s="3">
         <v>106000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>108000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>83000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>73000</v>
       </c>
     </row>
-    <row r="59" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
+        <v>838000</v>
+      </c>
+      <c r="E59" s="3">
+        <v>805000</v>
+      </c>
+      <c r="F59" s="3">
         <v>1747000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>1720000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>1759000</v>
       </c>
-      <c r="G59" s="3">
-        <v>1667000</v>
-      </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
+        <v>2682000</v>
+      </c>
+      <c r="J59" s="3">
         <v>1788000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>1776000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>1846000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>1909000</v>
       </c>
     </row>
-    <row r="60" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
+        <v>1335000</v>
+      </c>
+      <c r="E60" s="3">
+        <v>1333000</v>
+      </c>
+      <c r="F60" s="3">
         <v>2680000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>2657000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>2816000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>2713000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>2770000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>2833000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>2830000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>2808000</v>
       </c>
     </row>
-    <row r="61" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
+        <v>2658000</v>
+      </c>
+      <c r="E61" s="3">
+        <v>2570000</v>
+      </c>
+      <c r="F61" s="3">
         <v>7416000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>5316000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>5406000</v>
       </c>
-      <c r="G61" s="3">
-        <v>5561000</v>
-      </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
+        <v>5555000</v>
+      </c>
+      <c r="J61" s="3">
         <v>5611000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>5497000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>5516000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>5518000</v>
       </c>
     </row>
-    <row r="62" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
+        <v>774000</v>
+      </c>
+      <c r="E62" s="3">
+        <v>786000</v>
+      </c>
+      <c r="F62" s="3">
         <v>1480000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>1477000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>1457000</v>
       </c>
-      <c r="G62" s="3">
-        <v>1479000</v>
-      </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
+        <v>1485000</v>
+      </c>
+      <c r="J62" s="3">
         <v>1681000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>1778000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>1770000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>1782000</v>
       </c>
     </row>
-    <row r="63" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -2163,8 +2460,14 @@
       <c r="K63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -2192,8 +2495,14 @@
       <c r="K64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -2221,37 +2530,49 @@
       <c r="K65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
+        <v>4765000</v>
+      </c>
+      <c r="E66" s="3">
+        <v>4689000</v>
+      </c>
+      <c r="F66" s="3">
         <v>11576000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>9449000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>9678000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>9752000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>10063000</v>
-      </c>
-      <c r="I66" s="3">
-        <v>10111000</v>
-      </c>
-      <c r="J66" s="3">
-        <v>10118000</v>
       </c>
       <c r="K66" s="3">
         <v>10111000</v>
       </c>
-    </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L66" s="3">
+        <v>10118000</v>
+      </c>
+      <c r="M66" s="3">
+        <v>10111000</v>
+      </c>
+    </row>
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -2263,8 +2584,10 @@
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
-    </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L67" s="3"/>
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -2292,8 +2615,14 @@
       <c r="K68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -2321,16 +2650,22 @@
       <c r="K69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
       <c r="D70" s="3">
-        <v>275000</v>
+        <v>276000</v>
       </c>
       <c r="E70" s="3">
-        <v>275000</v>
+        <v>276000</v>
       </c>
       <c r="F70" s="3">
         <v>275000</v>
@@ -2345,13 +2680,19 @@
         <v>275000</v>
       </c>
       <c r="J70" s="3">
+        <v>275000</v>
+      </c>
+      <c r="K70" s="3">
+        <v>275000</v>
+      </c>
+      <c r="L70" s="3">
         <v>274000</v>
       </c>
-      <c r="K70" s="3">
+      <c r="M70" s="3">
         <v>274000</v>
       </c>
     </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -2379,37 +2720,49 @@
       <c r="K71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
+        <v>-463000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-421000</v>
+      </c>
+      <c r="F72" s="3">
         <v>967000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>1095000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>1080000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>1075000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>1095000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>1030000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>993000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>1031000</v>
       </c>
     </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -2437,8 +2790,14 @@
       <c r="K73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -2466,8 +2825,14 @@
       <c r="K74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -2495,37 +2860,49 @@
       <c r="K75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
+        <v>-34000</v>
+      </c>
+      <c r="E76" s="3">
+        <v>25000</v>
+      </c>
+      <c r="F76" s="3">
         <v>1372000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>1555000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>1489000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>1480000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>1445000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>1370000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>1323000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>1256000</v>
       </c>
     </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -2553,71 +2930,89 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
     </row>
-    <row r="81" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
-        <v>-120000</v>
+        <v>-44000</v>
       </c>
       <c r="E81" s="3">
+        <v>-439000</v>
+      </c>
+      <c r="F81" s="3">
+        <v>-128000</v>
+      </c>
+      <c r="G81" s="3">
         <v>15000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>5000</v>
       </c>
-      <c r="G81" s="3">
-        <v>-20000</v>
-      </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
+        <v>46000</v>
+      </c>
+      <c r="J81" s="3">
         <v>65000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>37000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-38000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>60000</v>
       </c>
     </row>
-    <row r="82" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -2629,37 +3024,45 @@
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
-    </row>
-    <row r="83" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L82" s="3"/>
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D83" s="3">
-        <v>461000</v>
+        <v>81000</v>
       </c>
       <c r="E83" s="3">
+        <v>559000</v>
+      </c>
+      <c r="F83" s="3">
         <v>155000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
+        <v>155000</v>
+      </c>
+      <c r="H83" s="3">
         <v>151000</v>
       </c>
-      <c r="G83" s="3">
-        <v>159000</v>
-      </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
+        <v>610000</v>
+      </c>
+      <c r="J83" s="3">
         <v>152000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>152000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>147000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>153000</v>
       </c>
     </row>
-    <row r="84" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -2687,8 +3090,14 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -2716,8 +3125,14 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -2745,8 +3160,14 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -2774,8 +3195,14 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -2803,37 +3230,49 @@
       <c r="K88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
-        <v>727000</v>
+        <v>-35000</v>
       </c>
       <c r="E89" s="3">
+        <v>694000</v>
+      </c>
+      <c r="F89" s="3">
+        <v>189000</v>
+      </c>
+      <c r="G89" s="3">
         <v>227000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>311000</v>
       </c>
-      <c r="G89" s="3">
-        <v>183000</v>
-      </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
+        <v>427000</v>
+      </c>
+      <c r="J89" s="3">
         <v>126000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>84000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>34000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>252000</v>
       </c>
     </row>
-    <row r="90" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -2845,37 +3284,45 @@
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
-    </row>
-    <row r="91" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L90" s="3"/>
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D91" s="3">
+        <v>-61000</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-71000</v>
+      </c>
+      <c r="F91" s="3">
         <v>-102000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-121000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-83000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-88000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-115000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-94000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-80000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-106000</v>
       </c>
     </row>
-    <row r="92" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -2903,8 +3350,14 @@
       <c r="K92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -2932,37 +3385,49 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
-        <v>-305000</v>
+        <v>-54000</v>
       </c>
       <c r="E94" s="3">
+        <v>-290000</v>
+      </c>
+      <c r="F94" s="3">
+        <v>-111000</v>
+      </c>
+      <c r="G94" s="3">
         <v>-108000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-86000</v>
       </c>
-      <c r="G94" s="3">
-        <v>-89000</v>
-      </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
+        <v>-387000</v>
+      </c>
+      <c r="J94" s="3">
         <v>-121000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-91000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-86000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-114000</v>
       </c>
     </row>
-    <row r="95" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -2974,8 +3439,10 @@
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
-    </row>
-    <row r="96" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L95" s="3"/>
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
@@ -3003,8 +3470,14 @@
       <c r="K96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -3032,8 +3505,14 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -3061,8 +3540,14 @@
       <c r="K98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -3090,91 +3575,115 @@
       <c r="K99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D100" s="3">
-        <v>1879000</v>
+        <v>80000</v>
       </c>
       <c r="E100" s="3">
+        <v>-839000</v>
+      </c>
+      <c r="F100" s="3">
+        <v>2145000</v>
+      </c>
+      <c r="G100" s="3">
         <v>-91000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-175000</v>
       </c>
-      <c r="G100" s="3">
-        <v>-92000</v>
-      </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
+        <v>1000</v>
+      </c>
+      <c r="J100" s="3">
         <v>100000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-8000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>1000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-18000</v>
       </c>
     </row>
-    <row r="101" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D101" s="3">
-        <v>-28000</v>
+        <v>-7000</v>
       </c>
       <c r="E101" s="3">
+        <v>-20000</v>
+      </c>
+      <c r="F101" s="3">
+        <v>-20000</v>
+      </c>
+      <c r="G101" s="3">
         <v>2000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>-10000</v>
       </c>
-      <c r="G101" s="3">
-        <v>-7000</v>
-      </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
+        <v>-50000</v>
+      </c>
+      <c r="J101" s="3">
         <v>-24000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-13000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-6000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-6000</v>
       </c>
     </row>
-    <row r="102" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
-        <v>2273000</v>
+        <v>-16000</v>
       </c>
       <c r="E102" s="3">
+        <v>-455000</v>
+      </c>
+      <c r="F102" s="3">
+        <v>2203000</v>
+      </c>
+      <c r="G102" s="3">
         <v>30000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>40000</v>
       </c>
-      <c r="G102" s="3">
-        <v>-5000</v>
-      </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="J102" s="3">
         <v>81000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-28000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-57000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>114000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/VYX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VYX_QTR_FIN.xlsx
@@ -653,174 +653,187 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:N102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>876000</v>
+      </c>
+      <c r="E8" s="3">
         <v>862000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3830000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2017000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1986000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1891000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3793000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1972000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1997000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1866000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2034000</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>685000</v>
+      </c>
+      <c r="E9" s="3">
         <v>666000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2868000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1390000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1448000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1425000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2815000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1481000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1526000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1455000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1531000</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>191000</v>
+      </c>
+      <c r="E10" s="3">
         <v>196000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>962000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>627000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>538000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>466000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>978000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>491000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>471000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>411000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>503000</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -834,43 +847,47 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>53000</v>
+      </c>
+      <c r="E12" s="3">
         <v>56000</v>
       </c>
-      <c r="E12" s="3">
-        <v>185000</v>
-      </c>
       <c r="F12" s="3">
+        <v>178000</v>
+      </c>
+      <c r="G12" s="3">
         <v>54000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>57000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>64000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>127000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>39000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>51000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>64000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>63000</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -904,54 +921,60 @@
       <c r="M13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>27000</v>
+      </c>
+      <c r="E14" s="3">
         <v>23000</v>
       </c>
-      <c r="E14" s="3">
-        <v>128000</v>
-      </c>
       <c r="F14" s="3">
+        <v>144000</v>
+      </c>
+      <c r="G14" s="3">
         <v>72000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>57000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>22000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>62000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>9000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>35000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>31000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>23000</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E15" s="3">
         <v>10000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>33000</v>
-      </c>
-      <c r="F15" s="3">
-        <v>16000</v>
       </c>
       <c r="G15" s="3">
         <v>16000</v>
@@ -960,22 +983,25 @@
         <v>16000</v>
       </c>
       <c r="I15" s="3">
+        <v>16000</v>
+      </c>
+      <c r="J15" s="3">
         <v>30000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>17000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>18000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>22000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>23000</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -986,78 +1012,85 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>880000</v>
+      </c>
+      <c r="E17" s="3">
         <v>858000</v>
       </c>
-      <c r="E17" s="3">
-        <v>3839000</v>
-      </c>
       <c r="F17" s="3">
+        <v>3848000</v>
+      </c>
+      <c r="G17" s="3">
         <v>1775000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1838000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1781000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3657000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1785000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1894000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1833000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1911000</v>
       </c>
     </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="E18" s="3">
         <v>4000</v>
       </c>
-      <c r="E18" s="3">
-        <v>-9000</v>
-      </c>
       <c r="F18" s="3">
+        <v>-18000</v>
+      </c>
+      <c r="G18" s="3">
         <v>242000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>148000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>110000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>136000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>187000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>103000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>33000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>123000</v>
       </c>
     </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1071,183 +1104,199 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3"/>
+    </row>
+    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-20000</v>
       </c>
-      <c r="E20" s="3">
-        <v>-79000</v>
-      </c>
       <c r="F20" s="3">
+        <v>-70000</v>
+      </c>
+      <c r="G20" s="3">
         <v>-44000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-8000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-3000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>99000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-1000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>1000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>9000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>113000</v>
       </c>
     </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>77000</v>
+      </c>
+      <c r="E21" s="3">
         <v>65000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>471000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>353000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>295000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>258000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>845000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>338000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>256000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>189000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>389000</v>
       </c>
     </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>41000</v>
+      </c>
+      <c r="E22" s="3">
         <v>39000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>294000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>85000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>91000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>83000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>366000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>74000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>67000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>63000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>64000</v>
       </c>
     </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>-50000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-55000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-382000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>113000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>49000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>24000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-131000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>112000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>37000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-21000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>172000</v>
       </c>
     </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>24000</v>
+      </c>
+      <c r="E24" s="3">
         <v>-14000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>204000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>236000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>30000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>14000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>72000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>43000</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
       <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3">
         <v>13000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>109000</v>
       </c>
     </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1281,78 +1330,87 @@
       <c r="M25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>-74000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-41000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-586000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-123000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>19000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>10000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-203000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>69000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>37000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-34000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>63000</v>
       </c>
     </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>-78000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-44000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-602000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-128000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>16000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>5000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-217000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>65000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>31000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-37000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>60000</v>
       </c>
     </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -1386,43 +1444,49 @@
       <c r="M28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D29" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
         <v>163000</v>
       </c>
-      <c r="F29" s="3">
-        <v>0</v>
-      </c>
       <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
         <v>-1000</v>
       </c>
-      <c r="H29" s="3">
-        <v>0</v>
-      </c>
       <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
         <v>263000</v>
       </c>
-      <c r="J29" s="3">
-        <v>0</v>
-      </c>
       <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3">
         <v>6000</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>-1000</v>
       </c>
-      <c r="M29" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -1456,8 +1520,11 @@
       <c r="M30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -1491,78 +1558,87 @@
       <c r="M31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E32" s="3">
         <v>20000</v>
       </c>
-      <c r="E32" s="3">
-        <v>79000</v>
-      </c>
       <c r="F32" s="3">
+        <v>70000</v>
+      </c>
+      <c r="G32" s="3">
         <v>44000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>8000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>3000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-99000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>1000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-1000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-9000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-113000</v>
       </c>
     </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
+        <v>-77000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-44000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-439000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-128000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>15000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>5000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>46000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>65000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>37000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-38000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>60000</v>
       </c>
     </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -1596,83 +1672,92 @@
       <c r="M34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
+        <v>-77000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-44000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-439000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-128000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>15000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>5000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>46000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>65000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>37000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-38000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>60000</v>
       </c>
     </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -1686,8 +1771,9 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="3"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -1701,43 +1787,47 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="3"/>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>204000</v>
+      </c>
+      <c r="E41" s="3">
         <v>246000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>262000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>675000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>547000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>519000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>221000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>434000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>398000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>412000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>447000</v>
       </c>
     </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
@@ -1771,148 +1861,163 @@
       <c r="M42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
+        <v>429000</v>
+      </c>
+      <c r="E43" s="3">
         <v>484000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>481000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>950000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>986000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1009000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>550000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1116000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1085000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1071000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>959000</v>
       </c>
     </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
+        <v>220000</v>
+      </c>
+      <c r="E44" s="3">
         <v>259000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>254000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>725000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>709000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>792000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>357000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>827000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>858000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>805000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>754000</v>
       </c>
     </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3">
+        <v>211000</v>
+      </c>
+      <c r="E45" s="3">
         <v>249000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>209000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>743000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>712000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>750000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1954000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>814000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>713000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>688000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>716000</v>
       </c>
     </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
+        <v>1064000</v>
+      </c>
+      <c r="E46" s="3">
         <v>1238000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1206000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>3093000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2954000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>3070000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>3082000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>3191000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>3054000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2976000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2876000</v>
       </c>
     </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
@@ -1946,78 +2051,87 @@
       <c r="M47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
-        <v>448000</v>
+        <v>438000</v>
       </c>
       <c r="E48" s="3">
         <v>448000</v>
       </c>
       <c r="F48" s="3">
+        <v>448000</v>
+      </c>
+      <c r="G48" s="3">
         <v>1029000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1030000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1034000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>499000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>997000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1039000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1075000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1122000</v>
       </c>
     </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
+        <v>2299000</v>
+      </c>
+      <c r="E49" s="3">
         <v>2316000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2331000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>5547000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>5608000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>5647000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2480000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>5756000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>5825000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>5879000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>5835000</v>
       </c>
     </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -2051,8 +2165,11 @@
       <c r="M50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -2086,43 +2203,49 @@
       <c r="M51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
-        <v>1005000</v>
+        <v>982000</v>
       </c>
       <c r="E52" s="3">
         <v>1005000</v>
       </c>
       <c r="F52" s="3">
+        <v>1005000</v>
+      </c>
+      <c r="G52" s="3">
         <v>3554000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1687000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1691000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>6342000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1839000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1838000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1785000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1808000</v>
       </c>
     </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -2156,43 +2279,49 @@
       <c r="M53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
+        <v>4783000</v>
+      </c>
+      <c r="E54" s="3">
         <v>5007000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>4990000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>13223000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>11279000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>11442000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>11507000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>11783000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>11756000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>11715000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>11641000</v>
       </c>
     </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -2206,8 +2335,9 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="3"/>
+    </row>
+    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -2221,43 +2351,47 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="3"/>
+    </row>
+    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
+        <v>478000</v>
+      </c>
+      <c r="E57" s="3">
         <v>482000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>505000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>820000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>832000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>952000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>594000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>876000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>949000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>901000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>826000</v>
       </c>
     </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
@@ -2265,174 +2399,189 @@
         <v>15000</v>
       </c>
       <c r="E58" s="3">
+        <v>15000</v>
+      </c>
+      <c r="F58" s="3">
         <v>23000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>113000</v>
-      </c>
-      <c r="G58" s="3">
-        <v>105000</v>
       </c>
       <c r="H58" s="3">
         <v>105000</v>
       </c>
       <c r="I58" s="3">
+        <v>105000</v>
+      </c>
+      <c r="J58" s="3">
         <v>110000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>106000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>108000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>83000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>73000</v>
       </c>
     </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
+        <v>761000</v>
+      </c>
+      <c r="E59" s="3">
         <v>838000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>805000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1747000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1720000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1759000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2682000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1788000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1776000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1846000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1909000</v>
       </c>
     </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
+        <v>1254000</v>
+      </c>
+      <c r="E60" s="3">
         <v>1335000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1333000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2680000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2657000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2816000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2713000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2770000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2833000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2830000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2808000</v>
       </c>
     </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
+        <v>2595000</v>
+      </c>
+      <c r="E61" s="3">
         <v>2658000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2570000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>7416000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>5316000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>5406000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>5555000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>5611000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>5497000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>5516000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>5518000</v>
       </c>
     </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
+        <v>745000</v>
+      </c>
+      <c r="E62" s="3">
         <v>774000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>786000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1480000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1477000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1457000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1485000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1681000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1778000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1770000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1782000</v>
       </c>
     </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -2466,8 +2615,11 @@
       <c r="M63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -2501,8 +2653,11 @@
       <c r="M64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -2536,43 +2691,49 @@
       <c r="M65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
+        <v>4592000</v>
+      </c>
+      <c r="E66" s="3">
         <v>4765000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4689000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>11576000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>9449000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>9678000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>9752000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>10063000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>10111000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>10118000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>10111000</v>
       </c>
     </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -2586,8 +2747,9 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="3"/>
+    </row>
+    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -2621,8 +2783,11 @@
       <c r="M68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -2656,8 +2821,11 @@
       <c r="M69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -2668,7 +2836,7 @@
         <v>276000</v>
       </c>
       <c r="F70" s="3">
-        <v>275000</v>
+        <v>276000</v>
       </c>
       <c r="G70" s="3">
         <v>275000</v>
@@ -2686,13 +2854,16 @@
         <v>275000</v>
       </c>
       <c r="L70" s="3">
-        <v>274000</v>
+        <v>275000</v>
       </c>
       <c r="M70" s="3">
         <v>274000</v>
       </c>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N70" s="3">
+        <v>274000</v>
+      </c>
+    </row>
+    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -2726,43 +2897,49 @@
       <c r="M71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
+        <v>-517000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-463000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-421000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>967000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1095000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1080000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1075000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1095000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1030000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>993000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1031000</v>
       </c>
     </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -2796,8 +2973,11 @@
       <c r="M73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -2831,8 +3011,11 @@
       <c r="M74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -2866,43 +3049,49 @@
       <c r="M75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
+        <v>-85000</v>
+      </c>
+      <c r="E76" s="3">
         <v>-34000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>25000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1372000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1555000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1489000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1480000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1445000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1370000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1323000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1256000</v>
       </c>
     </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -2936,83 +3125,92 @@
       <c r="M77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
     </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
+        <v>-77000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-44000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-439000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-128000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>15000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>5000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>46000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>65000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>37000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-38000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>60000</v>
       </c>
     </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -3026,43 +3224,47 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="3"/>
+    </row>
+    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D83" s="3">
+        <v>86000</v>
+      </c>
+      <c r="E83" s="3">
         <v>81000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>559000</v>
-      </c>
-      <c r="F83" s="3">
-        <v>155000</v>
       </c>
       <c r="G83" s="3">
         <v>155000</v>
       </c>
       <c r="H83" s="3">
+        <v>155000</v>
+      </c>
+      <c r="I83" s="3">
         <v>151000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>610000</v>
-      </c>
-      <c r="J83" s="3">
-        <v>152000</v>
       </c>
       <c r="K83" s="3">
         <v>152000</v>
       </c>
       <c r="L83" s="3">
+        <v>152000</v>
+      </c>
+      <c r="M83" s="3">
         <v>147000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>153000</v>
       </c>
     </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -3096,8 +3298,11 @@
       <c r="M84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -3131,8 +3336,11 @@
       <c r="M85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -3166,8 +3374,11 @@
       <c r="M86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -3201,8 +3412,11 @@
       <c r="M87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -3236,43 +3450,49 @@
       <c r="M88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
+        <v>62000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-35000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>694000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>189000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>227000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>311000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>427000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>126000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>84000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>34000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>252000</v>
       </c>
     </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -3286,43 +3506,47 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="3"/>
+    </row>
+    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D91" s="3">
+        <v>-64000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-61000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-71000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-102000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-121000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-83000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-88000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-115000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-94000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-80000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-106000</v>
       </c>
     </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -3356,8 +3580,11 @@
       <c r="M92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -3391,43 +3618,49 @@
       <c r="M93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
+        <v>-27000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-54000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-290000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-111000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-108000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-86000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-387000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-121000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-91000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-86000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-114000</v>
       </c>
     </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -3441,8 +3674,9 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="3"/>
+    </row>
+    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
@@ -3476,8 +3710,11 @@
       <c r="M96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -3511,8 +3748,11 @@
       <c r="M97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -3546,8 +3786,11 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -3581,43 +3824,49 @@
       <c r="M99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D100" s="3">
+        <v>-65000</v>
+      </c>
+      <c r="E100" s="3">
         <v>80000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-839000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>2145000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-91000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-175000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>1000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>100000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-8000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-18000</v>
       </c>
     </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
@@ -3625,65 +3874,71 @@
         <v>-7000</v>
       </c>
       <c r="E101" s="3">
-        <v>-20000</v>
+        <v>-7000</v>
       </c>
       <c r="F101" s="3">
         <v>-20000</v>
       </c>
       <c r="G101" s="3">
+        <v>-20000</v>
+      </c>
+      <c r="H101" s="3">
         <v>2000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-10000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-50000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-24000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-13000</v>
-      </c>
-      <c r="L101" s="3">
-        <v>-6000</v>
       </c>
       <c r="M101" s="3">
         <v>-6000</v>
       </c>
-    </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N101" s="3">
+        <v>-6000</v>
+      </c>
+    </row>
+    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
+        <v>-37000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-16000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-455000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>2203000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>30000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>40000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-9000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>81000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-28000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-57000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>114000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/VYX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VYX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="92">
   <si>
     <t>VYX</t>
   </si>
@@ -295,6 +295,9 @@
   </si>
   <si>
     <t xml:space="preserve">Change In Cash and Cash Equivalents </t>
+  </si>
+  <si>
+    <t>NA</t>
   </si>
 </sst>
 </file>
@@ -653,187 +656,200 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>876000</v>
+        <v>711000</v>
       </c>
       <c r="E8" s="3">
-        <v>862000</v>
+        <v>575000</v>
       </c>
       <c r="F8" s="3">
-        <v>3830000</v>
-      </c>
-      <c r="G8" s="3">
-        <v>2017000</v>
+        <v>858000</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="H8" s="3">
-        <v>1986000</v>
+        <v>809000</v>
       </c>
       <c r="I8" s="3">
-        <v>1891000</v>
+        <v>667000</v>
       </c>
       <c r="J8" s="3">
+        <v>906000</v>
+      </c>
+      <c r="K8" s="3">
         <v>3793000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1972000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1997000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1866000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2034000</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>685000</v>
+        <v>545000</v>
       </c>
       <c r="E9" s="3">
-        <v>666000</v>
+        <v>491000</v>
       </c>
       <c r="F9" s="3">
-        <v>2868000</v>
+        <v>652000</v>
       </c>
       <c r="G9" s="3">
-        <v>1390000</v>
+        <v>-1438000</v>
       </c>
       <c r="H9" s="3">
-        <v>1448000</v>
+        <v>611000</v>
       </c>
       <c r="I9" s="3">
-        <v>1425000</v>
+        <v>523000</v>
       </c>
       <c r="J9" s="3">
+        <v>682000</v>
+      </c>
+      <c r="K9" s="3">
         <v>2815000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1481000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1526000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1455000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1531000</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>191000</v>
+        <v>166000</v>
       </c>
       <c r="E10" s="3">
-        <v>196000</v>
+        <v>84000</v>
       </c>
       <c r="F10" s="3">
-        <v>962000</v>
+        <v>206000</v>
       </c>
       <c r="G10" s="3">
-        <v>627000</v>
+        <v>-626000</v>
       </c>
       <c r="H10" s="3">
-        <v>538000</v>
+        <v>198000</v>
       </c>
       <c r="I10" s="3">
-        <v>466000</v>
+        <v>144000</v>
       </c>
       <c r="J10" s="3">
+        <v>224000</v>
+      </c>
+      <c r="K10" s="3">
         <v>978000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>491000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>471000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>411000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>503000</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -848,46 +864,50 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>53000</v>
+        <v>34000</v>
       </c>
       <c r="E12" s="3">
-        <v>56000</v>
+        <v>30000</v>
       </c>
       <c r="F12" s="3">
-        <v>178000</v>
+        <v>54000</v>
       </c>
       <c r="G12" s="3">
-        <v>54000</v>
+        <v>1000</v>
       </c>
       <c r="H12" s="3">
-        <v>57000</v>
+        <v>29000</v>
       </c>
       <c r="I12" s="3">
+        <v>20000</v>
+      </c>
+      <c r="J12" s="3">
+        <v>49000</v>
+      </c>
+      <c r="K12" s="3">
+        <v>127000</v>
+      </c>
+      <c r="L12" s="3">
+        <v>39000</v>
+      </c>
+      <c r="M12" s="3">
+        <v>51000</v>
+      </c>
+      <c r="N12" s="3">
         <v>64000</v>
       </c>
-      <c r="J12" s="3">
-        <v>127000</v>
-      </c>
-      <c r="K12" s="3">
-        <v>39000</v>
-      </c>
-      <c r="L12" s="3">
-        <v>51000</v>
-      </c>
-      <c r="M12" s="3">
-        <v>64000</v>
-      </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>63000</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -924,84 +944,93 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>27000</v>
+        <v>2000</v>
       </c>
       <c r="E14" s="3">
+        <v>29000</v>
+      </c>
+      <c r="F14" s="3">
+        <v>34000</v>
+      </c>
+      <c r="G14" s="3">
+        <v>15000</v>
+      </c>
+      <c r="H14" s="3">
+        <v>28000</v>
+      </c>
+      <c r="I14" s="3">
+        <v>28000</v>
+      </c>
+      <c r="J14" s="3">
+        <v>7000</v>
+      </c>
+      <c r="K14" s="3">
+        <v>62000</v>
+      </c>
+      <c r="L14" s="3">
+        <v>9000</v>
+      </c>
+      <c r="M14" s="3">
+        <v>35000</v>
+      </c>
+      <c r="N14" s="3">
+        <v>31000</v>
+      </c>
+      <c r="O14" s="3">
         <v>23000</v>
       </c>
-      <c r="F14" s="3">
-        <v>144000</v>
-      </c>
-      <c r="G14" s="3">
-        <v>72000</v>
-      </c>
-      <c r="H14" s="3">
-        <v>57000</v>
-      </c>
-      <c r="I14" s="3">
-        <v>22000</v>
-      </c>
-      <c r="J14" s="3">
-        <v>62000</v>
-      </c>
-      <c r="K14" s="3">
-        <v>9000</v>
-      </c>
-      <c r="L14" s="3">
-        <v>35000</v>
-      </c>
-      <c r="M14" s="3">
-        <v>31000</v>
-      </c>
-      <c r="N14" s="3">
-        <v>23000</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>6000</v>
+        <v>70000</v>
       </c>
       <c r="E15" s="3">
-        <v>10000</v>
+        <v>86000</v>
       </c>
       <c r="F15" s="3">
-        <v>33000</v>
+        <v>81000</v>
       </c>
       <c r="G15" s="3">
-        <v>16000</v>
+        <v>91000</v>
       </c>
       <c r="H15" s="3">
-        <v>16000</v>
+        <v>155000</v>
       </c>
       <c r="I15" s="3">
-        <v>16000</v>
+        <v>155000</v>
       </c>
       <c r="J15" s="3">
+        <v>151000</v>
+      </c>
+      <c r="K15" s="3">
         <v>30000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>17000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>18000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>22000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>23000</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1013,84 +1042,91 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>687000</v>
+      </c>
+      <c r="E17" s="3">
+        <v>606000</v>
+      </c>
+      <c r="F17" s="3">
+        <v>820000</v>
+      </c>
+      <c r="G17" s="3">
+        <v>-1581000</v>
+      </c>
+      <c r="H17" s="3">
+        <v>758000</v>
+      </c>
+      <c r="I17" s="3">
+        <v>651000</v>
+      </c>
+      <c r="J17" s="3">
         <v>880000</v>
       </c>
-      <c r="E17" s="3">
-        <v>858000</v>
-      </c>
-      <c r="F17" s="3">
-        <v>3848000</v>
-      </c>
-      <c r="G17" s="3">
-        <v>1775000</v>
-      </c>
-      <c r="H17" s="3">
-        <v>1838000</v>
-      </c>
-      <c r="I17" s="3">
-        <v>1781000</v>
-      </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3657000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1785000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1894000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1833000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1911000</v>
       </c>
     </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>-4000</v>
+        <v>24000</v>
       </c>
       <c r="E18" s="3">
-        <v>4000</v>
+        <v>-31000</v>
       </c>
       <c r="F18" s="3">
-        <v>-18000</v>
+        <v>38000</v>
       </c>
       <c r="G18" s="3">
-        <v>242000</v>
+        <v>-483000</v>
       </c>
       <c r="H18" s="3">
-        <v>148000</v>
+        <v>51000</v>
       </c>
       <c r="I18" s="3">
-        <v>110000</v>
+        <v>16000</v>
       </c>
       <c r="J18" s="3">
+        <v>26000</v>
+      </c>
+      <c r="K18" s="3">
         <v>136000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>187000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>103000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>33000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>123000</v>
       </c>
     </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1105,198 +1141,214 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>-5000</v>
+        <v>16000</v>
       </c>
       <c r="E20" s="3">
-        <v>-20000</v>
+        <v>5000</v>
       </c>
       <c r="F20" s="3">
-        <v>-70000</v>
+        <v>21000</v>
       </c>
       <c r="G20" s="3">
-        <v>-44000</v>
+        <v>37000</v>
       </c>
       <c r="H20" s="3">
-        <v>-8000</v>
+        <v>24000</v>
       </c>
       <c r="I20" s="3">
-        <v>-3000</v>
+        <v>11000</v>
       </c>
       <c r="J20" s="3">
+        <v>6000</v>
+      </c>
+      <c r="K20" s="3">
         <v>99000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-1000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>9000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>113000</v>
       </c>
     </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>77000</v>
+        <v>78000</v>
       </c>
       <c r="E21" s="3">
-        <v>65000</v>
+        <v>50000</v>
       </c>
       <c r="F21" s="3">
-        <v>471000</v>
+        <v>98000</v>
       </c>
       <c r="G21" s="3">
-        <v>353000</v>
+        <v>-429000</v>
       </c>
       <c r="H21" s="3">
-        <v>295000</v>
+        <v>182000</v>
       </c>
       <c r="I21" s="3">
-        <v>258000</v>
+        <v>160000</v>
       </c>
       <c r="J21" s="3">
+        <v>171000</v>
+      </c>
+      <c r="K21" s="3">
         <v>845000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>338000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>256000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>189000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>389000</v>
       </c>
     </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>40000</v>
+      </c>
+      <c r="E22" s="3">
         <v>41000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>39000</v>
       </c>
-      <c r="F22" s="3">
-        <v>294000</v>
-      </c>
       <c r="G22" s="3">
-        <v>85000</v>
+        <v>35000</v>
       </c>
       <c r="H22" s="3">
+        <v>83000</v>
+      </c>
+      <c r="I22" s="3">
         <v>91000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>83000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>366000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>74000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>67000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>63000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>64000</v>
       </c>
     </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
-        <v>-50000</v>
+        <v>-32000</v>
       </c>
       <c r="E23" s="3">
-        <v>-55000</v>
+        <v>-105000</v>
       </c>
       <c r="F23" s="3">
-        <v>-382000</v>
+        <v>-54000</v>
       </c>
       <c r="G23" s="3">
-        <v>113000</v>
+        <v>-568000</v>
       </c>
       <c r="H23" s="3">
-        <v>49000</v>
+        <v>-79000</v>
       </c>
       <c r="I23" s="3">
-        <v>24000</v>
+        <v>-111000</v>
       </c>
       <c r="J23" s="3">
+        <v>-67000</v>
+      </c>
+      <c r="K23" s="3">
         <v>-131000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>112000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>37000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-21000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>172000</v>
       </c>
     </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
-        <v>24000</v>
+        <v>-1000</v>
       </c>
       <c r="E24" s="3">
+        <v>18000</v>
+      </c>
+      <c r="F24" s="3">
         <v>-14000</v>
       </c>
-      <c r="F24" s="3">
-        <v>204000</v>
-      </c>
       <c r="G24" s="3">
-        <v>236000</v>
+        <v>-76000</v>
       </c>
       <c r="H24" s="3">
-        <v>30000</v>
+        <v>187000</v>
       </c>
       <c r="I24" s="3">
-        <v>14000</v>
+        <v>8000</v>
       </c>
       <c r="J24" s="3">
+        <v>5000</v>
+      </c>
+      <c r="K24" s="3">
         <v>72000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>43000</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
-      </c>
       <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3">
         <v>13000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>109000</v>
       </c>
     </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1333,84 +1385,93 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
-        <v>-74000</v>
+        <v>-31000</v>
       </c>
       <c r="E26" s="3">
-        <v>-41000</v>
+        <v>-123000</v>
       </c>
       <c r="F26" s="3">
-        <v>-586000</v>
+        <v>-40000</v>
       </c>
       <c r="G26" s="3">
-        <v>-123000</v>
+        <v>-492000</v>
       </c>
       <c r="H26" s="3">
-        <v>19000</v>
+        <v>-266000</v>
       </c>
       <c r="I26" s="3">
-        <v>10000</v>
+        <v>-119000</v>
       </c>
       <c r="J26" s="3">
+        <v>-72000</v>
+      </c>
+      <c r="K26" s="3">
         <v>-203000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>69000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>37000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-34000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>63000</v>
       </c>
     </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
-        <v>-78000</v>
+        <v>1078000</v>
       </c>
       <c r="E27" s="3">
+        <v>-77000</v>
+      </c>
+      <c r="F27" s="3">
         <v>-44000</v>
       </c>
-      <c r="F27" s="3">
-        <v>-602000</v>
-      </c>
       <c r="G27" s="3">
-        <v>-128000</v>
+        <v>-331000</v>
       </c>
       <c r="H27" s="3">
-        <v>16000</v>
+        <v>-133000</v>
       </c>
       <c r="I27" s="3">
-        <v>5000</v>
+        <v>13000</v>
       </c>
       <c r="J27" s="3">
+        <v>3000</v>
+      </c>
+      <c r="K27" s="3">
         <v>-217000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>65000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>31000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-37000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>60000</v>
       </c>
     </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -1447,46 +1508,52 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D29" s="3">
-        <v>1000</v>
+        <v>1113000</v>
       </c>
       <c r="E29" s="3">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="F29" s="3">
-        <v>163000</v>
+        <v>-1000</v>
       </c>
       <c r="G29" s="3">
-        <v>0</v>
+        <v>164000</v>
       </c>
       <c r="H29" s="3">
+        <v>138000</v>
+      </c>
+      <c r="I29" s="3">
+        <v>136000</v>
+      </c>
+      <c r="J29" s="3">
+        <v>79000</v>
+      </c>
+      <c r="K29" s="3">
+        <v>263000</v>
+      </c>
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3">
+        <v>6000</v>
+      </c>
+      <c r="N29" s="3">
         <v>-1000</v>
       </c>
-      <c r="I29" s="3">
-        <v>0</v>
-      </c>
-      <c r="J29" s="3">
-        <v>263000</v>
-      </c>
-      <c r="K29" s="3">
-        <v>0</v>
-      </c>
-      <c r="L29" s="3">
-        <v>6000</v>
-      </c>
-      <c r="M29" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="N29" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -1523,8 +1590,11 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -1561,84 +1631,93 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
-        <v>5000</v>
+        <v>-16000</v>
       </c>
       <c r="E32" s="3">
-        <v>20000</v>
+        <v>-5000</v>
       </c>
       <c r="F32" s="3">
-        <v>70000</v>
+        <v>-21000</v>
       </c>
       <c r="G32" s="3">
-        <v>44000</v>
+        <v>-37000</v>
       </c>
       <c r="H32" s="3">
-        <v>8000</v>
+        <v>-24000</v>
       </c>
       <c r="I32" s="3">
-        <v>3000</v>
+        <v>-11000</v>
       </c>
       <c r="J32" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="K32" s="3">
         <v>-99000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>1000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-9000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-113000</v>
       </c>
     </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
-        <v>-77000</v>
+        <v>1082000</v>
       </c>
       <c r="E33" s="3">
-        <v>-44000</v>
+        <v>-73000</v>
       </c>
       <c r="F33" s="3">
-        <v>-439000</v>
+        <v>-40000</v>
       </c>
       <c r="G33" s="3">
-        <v>-128000</v>
+        <v>-327000</v>
       </c>
       <c r="H33" s="3">
-        <v>15000</v>
+        <v>-129000</v>
       </c>
       <c r="I33" s="3">
-        <v>5000</v>
+        <v>17000</v>
       </c>
       <c r="J33" s="3">
+        <v>7000</v>
+      </c>
+      <c r="K33" s="3">
         <v>46000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>65000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>37000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-38000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>60000</v>
       </c>
     </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -1675,89 +1754,98 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
-        <v>-77000</v>
+        <v>1082000</v>
       </c>
       <c r="E35" s="3">
-        <v>-44000</v>
+        <v>-73000</v>
       </c>
       <c r="F35" s="3">
-        <v>-439000</v>
+        <v>-40000</v>
       </c>
       <c r="G35" s="3">
-        <v>-128000</v>
+        <v>-327000</v>
       </c>
       <c r="H35" s="3">
-        <v>15000</v>
+        <v>-129000</v>
       </c>
       <c r="I35" s="3">
-        <v>5000</v>
+        <v>17000</v>
       </c>
       <c r="J35" s="3">
+        <v>7000</v>
+      </c>
+      <c r="K35" s="3">
         <v>46000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>65000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>37000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-38000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>60000</v>
       </c>
     </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
     </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -1772,8 +1860,9 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -1788,46 +1877,50 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>795000</v>
+      </c>
+      <c r="E41" s="3">
         <v>204000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>246000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>262000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>675000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>547000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>519000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>221000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>434000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>398000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>412000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>447000</v>
       </c>
     </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
@@ -1844,13 +1937,13 @@
         <v>0</v>
       </c>
       <c r="H42" s="3">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="I42" s="3">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="J42" s="3">
-        <v>0</v>
+        <v>33000</v>
       </c>
       <c r="K42" s="3">
         <v>0</v>
@@ -1864,183 +1957,198 @@
       <c r="N42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
+        <v>623000</v>
+      </c>
+      <c r="E43" s="3">
         <v>429000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>484000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>481000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>950000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>986000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1009000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>550000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1116000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1085000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1071000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>959000</v>
       </c>
     </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
+        <v>208000</v>
+      </c>
+      <c r="E44" s="3">
         <v>220000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>259000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>254000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>725000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>709000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>792000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>357000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>827000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>858000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>805000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>754000</v>
       </c>
     </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D45" s="3">
-        <v>211000</v>
+      <c r="D45" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="E45" s="3">
-        <v>249000</v>
+        <v>1000</v>
       </c>
       <c r="F45" s="3">
-        <v>209000</v>
+        <v>5000</v>
       </c>
       <c r="G45" s="3">
-        <v>743000</v>
+        <v>188000</v>
       </c>
       <c r="H45" s="3">
-        <v>712000</v>
+        <v>1000</v>
       </c>
       <c r="I45" s="3">
-        <v>750000</v>
+        <v>1000</v>
       </c>
       <c r="J45" s="3">
+        <v>460000</v>
+      </c>
+      <c r="K45" s="3">
         <v>1954000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>814000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>713000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>688000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>716000</v>
       </c>
     </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
+        <v>1825000</v>
+      </c>
+      <c r="E46" s="3">
         <v>1064000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1238000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1206000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>3093000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2954000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>3070000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>3082000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>3191000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>3054000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2976000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2876000</v>
       </c>
     </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="H47" s="3">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="I47" s="3">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="J47" s="3">
-        <v>0</v>
+        <v>11000</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -2054,84 +2162,93 @@
       <c r="N47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
+        <v>429000</v>
+      </c>
+      <c r="E48" s="3">
         <v>438000</v>
-      </c>
-      <c r="E48" s="3">
-        <v>448000</v>
       </c>
       <c r="F48" s="3">
         <v>448000</v>
       </c>
       <c r="G48" s="3">
+        <v>448000</v>
+      </c>
+      <c r="H48" s="3">
         <v>1029000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1030000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1034000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>499000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>997000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1039000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1075000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1122000</v>
       </c>
     </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
-        <v>2299000</v>
+        <v>1934000</v>
       </c>
       <c r="E49" s="3">
-        <v>2316000</v>
+        <v>2785000</v>
       </c>
       <c r="F49" s="3">
-        <v>2331000</v>
+        <v>2803000</v>
       </c>
       <c r="G49" s="3">
-        <v>5547000</v>
+        <v>2817000</v>
       </c>
       <c r="H49" s="3">
-        <v>5608000</v>
+        <v>6119000</v>
       </c>
       <c r="I49" s="3">
+        <v>6181000</v>
+      </c>
+      <c r="J49" s="3">
         <v>5647000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2480000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>5756000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>5825000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>5879000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>5835000</v>
       </c>
     </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -2168,8 +2285,11 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -2206,46 +2326,52 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
-        <v>982000</v>
+        <v>261000</v>
       </c>
       <c r="E52" s="3">
-        <v>1005000</v>
+        <v>252000</v>
       </c>
       <c r="F52" s="3">
-        <v>1005000</v>
+        <v>283000</v>
       </c>
       <c r="G52" s="3">
-        <v>3554000</v>
+        <v>280000</v>
       </c>
       <c r="H52" s="3">
-        <v>1687000</v>
+        <v>2550000</v>
       </c>
       <c r="I52" s="3">
-        <v>1691000</v>
+        <v>523000</v>
       </c>
       <c r="J52" s="3">
+        <v>1085000</v>
+      </c>
+      <c r="K52" s="3">
         <v>6342000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1839000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1838000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1785000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1808000</v>
       </c>
     </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -2282,46 +2408,52 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
+        <v>4674000</v>
+      </c>
+      <c r="E54" s="3">
         <v>4783000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>5007000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>4990000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>13223000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>11279000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>11442000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>11507000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>11783000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>11756000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>11715000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>11641000</v>
       </c>
     </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -2336,8 +2468,9 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -2352,236 +2485,255 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
+        <v>400000</v>
+      </c>
+      <c r="E57" s="3">
         <v>478000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>482000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>505000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>820000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>832000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>952000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>594000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>876000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>949000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>901000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>826000</v>
       </c>
     </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="E58" s="3">
         <v>15000</v>
       </c>
       <c r="F58" s="3">
-        <v>23000</v>
+        <v>15000</v>
       </c>
       <c r="G58" s="3">
+        <v>67000</v>
+      </c>
+      <c r="H58" s="3">
         <v>113000</v>
-      </c>
-      <c r="H58" s="3">
-        <v>105000</v>
       </c>
       <c r="I58" s="3">
         <v>105000</v>
       </c>
       <c r="J58" s="3">
+        <v>105000</v>
+      </c>
+      <c r="K58" s="3">
         <v>110000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>106000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>108000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>83000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>73000</v>
       </c>
     </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
-        <v>761000</v>
+        <v>1008000</v>
       </c>
       <c r="E59" s="3">
-        <v>838000</v>
+        <v>668000</v>
       </c>
       <c r="F59" s="3">
-        <v>805000</v>
+        <v>738000</v>
       </c>
       <c r="G59" s="3">
-        <v>1747000</v>
+        <v>612000</v>
       </c>
       <c r="H59" s="3">
-        <v>1720000</v>
+        <v>1429000</v>
       </c>
       <c r="I59" s="3">
-        <v>1759000</v>
+        <v>1512000</v>
       </c>
       <c r="J59" s="3">
+        <v>1536000</v>
+      </c>
+      <c r="K59" s="3">
         <v>2682000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1788000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1776000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1846000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1909000</v>
       </c>
     </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
+        <v>1527000</v>
+      </c>
+      <c r="E60" s="3">
         <v>1254000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1335000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1333000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2680000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2657000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2816000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2713000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2770000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2833000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2830000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2808000</v>
       </c>
     </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
-        <v>2595000</v>
+        <v>1351000</v>
       </c>
       <c r="E61" s="3">
-        <v>2658000</v>
+        <v>2847000</v>
       </c>
       <c r="F61" s="3">
-        <v>2570000</v>
+        <v>2917000</v>
       </c>
       <c r="G61" s="3">
-        <v>7416000</v>
+        <v>2824000</v>
       </c>
       <c r="H61" s="3">
-        <v>5316000</v>
+        <v>7743000</v>
       </c>
       <c r="I61" s="3">
-        <v>5406000</v>
+        <v>5660000</v>
       </c>
       <c r="J61" s="3">
+        <v>5746000</v>
+      </c>
+      <c r="K61" s="3">
         <v>5555000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>5611000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>5497000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>5516000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>5518000</v>
       </c>
     </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
-        <v>745000</v>
+        <v>293000</v>
       </c>
       <c r="E62" s="3">
-        <v>774000</v>
+        <v>276000</v>
       </c>
       <c r="F62" s="3">
-        <v>786000</v>
+        <v>292000</v>
       </c>
       <c r="G62" s="3">
-        <v>1480000</v>
+        <v>303000</v>
       </c>
       <c r="H62" s="3">
-        <v>1477000</v>
+        <v>360000</v>
       </c>
       <c r="I62" s="3">
-        <v>1457000</v>
+        <v>373000</v>
       </c>
       <c r="J62" s="3">
+        <v>364000</v>
+      </c>
+      <c r="K62" s="3">
         <v>1485000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1681000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1778000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1770000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1782000</v>
       </c>
     </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -2618,8 +2770,11 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -2656,8 +2811,11 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -2694,46 +2852,52 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
-        <v>4592000</v>
+        <v>3387000</v>
       </c>
       <c r="E66" s="3">
-        <v>4765000</v>
+        <v>4594000</v>
       </c>
       <c r="F66" s="3">
+        <v>4767000</v>
+      </c>
+      <c r="G66" s="3">
         <v>4689000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>11576000</v>
       </c>
-      <c r="H66" s="3">
-        <v>9449000</v>
-      </c>
       <c r="I66" s="3">
-        <v>9678000</v>
+        <v>9450000</v>
       </c>
       <c r="J66" s="3">
+        <v>9679000</v>
+      </c>
+      <c r="K66" s="3">
         <v>9752000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>10063000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>10111000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>10118000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>10111000</v>
       </c>
     </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -2748,8 +2912,9 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -2786,8 +2951,11 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -2824,8 +2992,11 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -2839,7 +3010,7 @@
         <v>276000</v>
       </c>
       <c r="G70" s="3">
-        <v>275000</v>
+        <v>276000</v>
       </c>
       <c r="H70" s="3">
         <v>275000</v>
@@ -2857,13 +3028,16 @@
         <v>275000</v>
       </c>
       <c r="M70" s="3">
-        <v>274000</v>
+        <v>275000</v>
       </c>
       <c r="N70" s="3">
         <v>274000</v>
       </c>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O70" s="3">
+        <v>274000</v>
+      </c>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -2900,46 +3074,52 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
+        <v>561000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-517000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-463000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-421000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>967000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1095000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1080000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1075000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1095000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1030000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>993000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1031000</v>
       </c>
     </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -2976,8 +3156,11 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -3014,8 +3197,11 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -3052,46 +3238,52 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
+        <v>1013000</v>
+      </c>
+      <c r="E76" s="3">
         <v>-85000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-34000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>25000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1372000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1555000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1489000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1480000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1445000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1370000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1323000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1256000</v>
       </c>
     </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -3128,89 +3320,98 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
     </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
-        <v>-77000</v>
+        <v>1082000</v>
       </c>
       <c r="E81" s="3">
-        <v>-44000</v>
+        <v>-73000</v>
       </c>
       <c r="F81" s="3">
-        <v>-439000</v>
+        <v>-40000</v>
       </c>
       <c r="G81" s="3">
-        <v>-128000</v>
+        <v>-327000</v>
       </c>
       <c r="H81" s="3">
-        <v>15000</v>
+        <v>-129000</v>
       </c>
       <c r="I81" s="3">
-        <v>5000</v>
+        <v>17000</v>
       </c>
       <c r="J81" s="3">
+        <v>7000</v>
+      </c>
+      <c r="K81" s="3">
         <v>46000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>65000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>37000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-38000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>60000</v>
       </c>
     </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -3225,46 +3426,50 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D83" s="3">
-        <v>86000</v>
+        <v>155000</v>
       </c>
       <c r="E83" s="3">
-        <v>81000</v>
+        <v>137000</v>
       </c>
       <c r="F83" s="3">
-        <v>559000</v>
+        <v>134000</v>
       </c>
       <c r="G83" s="3">
-        <v>155000</v>
-      </c>
-      <c r="H83" s="3">
-        <v>155000</v>
+        <v>-10000</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="I83" s="3">
-        <v>151000</v>
+        <v>107000</v>
       </c>
       <c r="J83" s="3">
+        <v>106000</v>
+      </c>
+      <c r="K83" s="3">
         <v>610000</v>
-      </c>
-      <c r="K83" s="3">
-        <v>152000</v>
       </c>
       <c r="L83" s="3">
         <v>152000</v>
       </c>
       <c r="M83" s="3">
+        <v>152000</v>
+      </c>
+      <c r="N83" s="3">
         <v>147000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>153000</v>
       </c>
     </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -3301,8 +3506,11 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -3339,8 +3547,11 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -3377,8 +3588,11 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -3415,8 +3629,11 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -3453,46 +3670,52 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
+        <v>11000</v>
+      </c>
+      <c r="E89" s="3">
         <v>62000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-35000</v>
       </c>
-      <c r="F89" s="3">
-        <v>694000</v>
-      </c>
       <c r="G89" s="3">
+        <v>-33000</v>
+      </c>
+      <c r="H89" s="3">
         <v>189000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>227000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>311000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>427000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>126000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>84000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>34000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>252000</v>
       </c>
     </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -3507,46 +3730,50 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D91" s="3">
-        <v>-64000</v>
+        <v>-2000</v>
       </c>
       <c r="E91" s="3">
-        <v>-61000</v>
+        <v>-13000</v>
       </c>
       <c r="F91" s="3">
-        <v>-71000</v>
+        <v>-8000</v>
       </c>
       <c r="G91" s="3">
-        <v>-102000</v>
+        <v>-18000</v>
       </c>
       <c r="H91" s="3">
-        <v>-121000</v>
+        <v>-42000</v>
       </c>
       <c r="I91" s="3">
-        <v>-83000</v>
+        <v>-51000</v>
       </c>
       <c r="J91" s="3">
+        <v>-19000</v>
+      </c>
+      <c r="K91" s="3">
         <v>-88000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-115000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-94000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-80000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-106000</v>
       </c>
     </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -3583,8 +3810,11 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -3621,46 +3851,52 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
+        <v>2098000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-27000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-54000</v>
       </c>
-      <c r="F94" s="3">
-        <v>-290000</v>
-      </c>
       <c r="G94" s="3">
+        <v>15000</v>
+      </c>
+      <c r="H94" s="3">
         <v>-111000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-108000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-86000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-387000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-121000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-91000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-86000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-114000</v>
       </c>
     </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -3675,31 +3911,32 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -3713,8 +3950,11 @@
       <c r="N96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -3751,8 +3991,11 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -3789,8 +4032,11 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -3827,118 +4073,130 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D100" s="3">
+        <v>-1511000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-65000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>80000</v>
       </c>
-      <c r="F100" s="3">
-        <v>-839000</v>
-      </c>
       <c r="G100" s="3">
+        <v>-2718000</v>
+      </c>
+      <c r="H100" s="3">
         <v>2145000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-91000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-175000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>1000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>100000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-8000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>1000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-18000</v>
       </c>
     </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D101" s="3">
+        <v>-20000</v>
+      </c>
+      <c r="E101" s="3">
+        <v>2000</v>
+      </c>
+      <c r="F101" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="G101" s="3">
         <v>-7000</v>
       </c>
-      <c r="E101" s="3">
-        <v>-7000</v>
-      </c>
-      <c r="F101" s="3">
-        <v>-20000</v>
-      </c>
-      <c r="G101" s="3">
-        <v>-20000</v>
-      </c>
-      <c r="H101" s="3">
-        <v>2000</v>
+      <c r="H101" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="I101" s="3">
-        <v>-10000</v>
+        <v>-13000</v>
       </c>
       <c r="J101" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="K101" s="3">
         <v>-50000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-24000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-13000</v>
-      </c>
-      <c r="M101" s="3">
-        <v>-6000</v>
       </c>
       <c r="N101" s="3">
         <v>-6000</v>
       </c>
-    </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O101" s="3">
+        <v>-6000</v>
+      </c>
+    </row>
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
+        <v>593000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-37000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-16000</v>
       </c>
-      <c r="F102" s="3">
-        <v>-455000</v>
-      </c>
       <c r="G102" s="3">
+        <v>-2728000</v>
+      </c>
+      <c r="H102" s="3">
         <v>2203000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>30000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>40000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-9000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>81000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-28000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-57000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>114000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/VYX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VYX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="92">
   <si>
     <t>VYX</t>
   </si>
@@ -656,200 +656,212 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>682000</v>
+      </c>
+      <c r="E8" s="3">
         <v>711000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>575000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>858000</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>91</v>
-      </c>
       <c r="H8" s="3">
+        <v>796000</v>
+      </c>
+      <c r="I8" s="3">
         <v>809000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>667000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>906000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3793000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1972000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1997000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1866000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2034000</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>518000</v>
+      </c>
+      <c r="E9" s="3">
         <v>545000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>491000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>652000</v>
       </c>
-      <c r="G9" s="3">
-        <v>-1438000</v>
-      </c>
       <c r="H9" s="3">
+        <v>642000</v>
+      </c>
+      <c r="I9" s="3">
         <v>611000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>523000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>682000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2815000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1481000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1526000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1455000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1531000</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>164000</v>
+      </c>
+      <c r="E10" s="3">
         <v>166000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>84000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>206000</v>
       </c>
-      <c r="G10" s="3">
-        <v>-626000</v>
-      </c>
       <c r="H10" s="3">
+        <v>154000</v>
+      </c>
+      <c r="I10" s="3">
         <v>198000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>144000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>224000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>978000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>491000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>471000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>411000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>503000</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -865,49 +877,53 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>29000</v>
+      </c>
+      <c r="E12" s="3">
         <v>34000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>30000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>54000</v>
       </c>
-      <c r="G12" s="3">
-        <v>1000</v>
-      </c>
       <c r="H12" s="3">
+        <v>30000</v>
+      </c>
+      <c r="I12" s="3">
         <v>29000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>20000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>49000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>127000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>39000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>51000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>64000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>63000</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -947,90 +963,99 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>28000</v>
+      </c>
+      <c r="E14" s="3">
         <v>2000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>29000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>34000</v>
       </c>
-      <c r="G14" s="3">
-        <v>15000</v>
-      </c>
       <c r="H14" s="3">
-        <v>28000</v>
+        <v>121000</v>
       </c>
       <c r="I14" s="3">
         <v>28000</v>
       </c>
       <c r="J14" s="3">
+        <v>28000</v>
+      </c>
+      <c r="K14" s="3">
         <v>7000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>62000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>9000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>35000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>31000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>23000</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>39500</v>
+      </c>
+      <c r="E15" s="3">
         <v>70000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>86000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>81000</v>
       </c>
-      <c r="G15" s="3">
-        <v>91000</v>
-      </c>
       <c r="H15" s="3">
-        <v>155000</v>
+        <v>105800</v>
       </c>
       <c r="I15" s="3">
         <v>155000</v>
       </c>
       <c r="J15" s="3">
+        <v>155000</v>
+      </c>
+      <c r="K15" s="3">
         <v>151000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>30000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>17000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>18000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>22000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>23000</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1043,90 +1068,97 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>640000</v>
+      </c>
+      <c r="E17" s="3">
         <v>687000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>606000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>820000</v>
       </c>
-      <c r="G17" s="3">
-        <v>-1581000</v>
-      </c>
       <c r="H17" s="3">
+        <v>888000</v>
+      </c>
+      <c r="I17" s="3">
         <v>758000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>651000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>880000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3657000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1785000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1894000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1833000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1911000</v>
       </c>
     </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>42000</v>
+      </c>
+      <c r="E18" s="3">
         <v>24000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-31000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>38000</v>
       </c>
-      <c r="G18" s="3">
-        <v>-483000</v>
-      </c>
       <c r="H18" s="3">
+        <v>-92000</v>
+      </c>
+      <c r="I18" s="3">
         <v>51000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>16000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>26000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>136000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>187000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>103000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>33000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>123000</v>
       </c>
     </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1142,213 +1174,229 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>12000</v>
+      </c>
+      <c r="E20" s="3">
         <v>16000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>5000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>21000</v>
       </c>
-      <c r="G20" s="3">
-        <v>37000</v>
-      </c>
       <c r="H20" s="3">
+        <v>39000</v>
+      </c>
+      <c r="I20" s="3">
         <v>24000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>11000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>6000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>99000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-1000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>1000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>9000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>113000</v>
       </c>
     </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>69500</v>
+      </c>
+      <c r="E21" s="3">
         <v>78000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>50000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>98000</v>
       </c>
-      <c r="G21" s="3">
-        <v>-429000</v>
-      </c>
       <c r="H21" s="3">
+        <v>-25300</v>
+      </c>
+      <c r="I21" s="3">
         <v>182000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>160000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>171000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>845000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>338000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>256000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>189000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>389000</v>
       </c>
     </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>14000</v>
+      </c>
+      <c r="E22" s="3">
         <v>40000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>41000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>39000</v>
       </c>
-      <c r="G22" s="3">
-        <v>35000</v>
-      </c>
       <c r="H22" s="3">
+        <v>37000</v>
+      </c>
+      <c r="I22" s="3">
         <v>83000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>91000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>83000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>366000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>74000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>67000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>63000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>64000</v>
       </c>
     </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-32000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-105000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-54000</v>
       </c>
-      <c r="G23" s="3">
-        <v>-568000</v>
-      </c>
       <c r="H23" s="3">
+        <v>-288000</v>
+      </c>
+      <c r="I23" s="3">
         <v>-79000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-111000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-67000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-131000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>112000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>37000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-21000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>172000</v>
       </c>
     </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E24" s="3">
         <v>-1000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>18000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-14000</v>
       </c>
-      <c r="G24" s="3">
-        <v>-76000</v>
-      </c>
       <c r="H24" s="3">
+        <v>-16000</v>
+      </c>
+      <c r="I24" s="3">
         <v>187000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>8000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>5000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>72000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>43000</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
-      </c>
       <c r="N24" s="3">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3">
         <v>13000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>109000</v>
       </c>
     </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1388,90 +1436,99 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-31000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-123000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-40000</v>
       </c>
-      <c r="G26" s="3">
-        <v>-492000</v>
-      </c>
       <c r="H26" s="3">
+        <v>-272000</v>
+      </c>
+      <c r="I26" s="3">
         <v>-266000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-119000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-72000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-203000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>69000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>37000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-34000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>63000</v>
       </c>
     </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="E27" s="3">
         <v>1078000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-77000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-44000</v>
       </c>
-      <c r="G27" s="3">
-        <v>-331000</v>
-      </c>
       <c r="H27" s="3">
+        <v>-322000</v>
+      </c>
+      <c r="I27" s="3">
         <v>-133000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>13000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>3000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-217000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>65000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>31000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-37000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>60000</v>
       </c>
     </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -1511,49 +1568,55 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D29" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E29" s="3">
         <v>1113000</v>
       </c>
-      <c r="E29" s="3">
+      <c r="F29" s="3">
         <v>50000</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>-1000</v>
       </c>
-      <c r="G29" s="3">
-        <v>164000</v>
-      </c>
       <c r="H29" s="3">
+        <v>-47000</v>
+      </c>
+      <c r="I29" s="3">
         <v>138000</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>136000</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>79000</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>263000</v>
       </c>
-      <c r="L29" s="3">
-        <v>0</v>
-      </c>
       <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3">
         <v>6000</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>-1000</v>
       </c>
-      <c r="O29" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -1593,8 +1656,11 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -1634,90 +1700,99 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-16000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-5000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-21000</v>
       </c>
-      <c r="G32" s="3">
-        <v>-37000</v>
-      </c>
       <c r="H32" s="3">
+        <v>-39000</v>
+      </c>
+      <c r="I32" s="3">
         <v>-24000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-11000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-6000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-99000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>1000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-1000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-9000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-113000</v>
       </c>
     </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="E33" s="3">
         <v>1082000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-73000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-40000</v>
       </c>
-      <c r="G33" s="3">
-        <v>-327000</v>
-      </c>
       <c r="H33" s="3">
+        <v>-318000</v>
+      </c>
+      <c r="I33" s="3">
         <v>-129000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>17000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>7000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>46000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>65000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>37000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-38000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>60000</v>
       </c>
     </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -1757,95 +1832,104 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="E35" s="3">
         <v>1082000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-73000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-40000</v>
       </c>
-      <c r="G35" s="3">
-        <v>-327000</v>
-      </c>
       <c r="H35" s="3">
+        <v>-318000</v>
+      </c>
+      <c r="I35" s="3">
         <v>-129000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>17000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>7000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>46000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>65000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>37000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-38000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>60000</v>
       </c>
     </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
     </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -1861,8 +1945,9 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -1878,49 +1963,53 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>724000</v>
+      </c>
+      <c r="E41" s="3">
         <v>795000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>204000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>246000</v>
       </c>
-      <c r="G41" s="3">
-        <v>262000</v>
-      </c>
       <c r="H41" s="3">
+        <v>259000</v>
+      </c>
+      <c r="I41" s="3">
         <v>675000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>547000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>519000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>221000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>434000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>398000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>412000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>447000</v>
       </c>
     </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
@@ -1937,17 +2026,17 @@
         <v>0</v>
       </c>
       <c r="H42" s="3">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="I42" s="3">
         <v>20000</v>
       </c>
       <c r="J42" s="3">
+        <v>20000</v>
+      </c>
+      <c r="K42" s="3">
         <v>33000</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
       <c r="L42" s="3">
         <v>0</v>
       </c>
@@ -1960,49 +2049,55 @@
       <c r="O42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
+        <v>539000</v>
+      </c>
+      <c r="E43" s="3">
         <v>623000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>429000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>484000</v>
       </c>
-      <c r="G43" s="3">
-        <v>481000</v>
-      </c>
       <c r="H43" s="3">
+        <v>414000</v>
+      </c>
+      <c r="I43" s="3">
         <v>950000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>986000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1009000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>550000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1116000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1085000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1071000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>959000</v>
       </c>
     </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
@@ -2010,122 +2105,131 @@
         <v>208000</v>
       </c>
       <c r="E44" s="3">
+        <v>208000</v>
+      </c>
+      <c r="F44" s="3">
         <v>220000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>259000</v>
       </c>
-      <c r="G44" s="3">
-        <v>254000</v>
-      </c>
       <c r="H44" s="3">
+        <v>250000</v>
+      </c>
+      <c r="I44" s="3">
         <v>725000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>709000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>792000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>357000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>827000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>858000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>805000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>754000</v>
       </c>
     </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="E45" s="3">
+      <c r="E45" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F45" s="3">
         <v>1000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>5000</v>
       </c>
-      <c r="G45" s="3">
-        <v>188000</v>
-      </c>
       <c r="H45" s="3">
-        <v>1000</v>
+        <v>89000</v>
       </c>
       <c r="I45" s="3">
         <v>1000</v>
       </c>
       <c r="J45" s="3">
+        <v>1000</v>
+      </c>
+      <c r="K45" s="3">
         <v>460000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1954000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>814000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>713000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>688000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>716000</v>
       </c>
     </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
+        <v>1671000</v>
+      </c>
+      <c r="E46" s="3">
         <v>1825000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1064000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1238000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1206000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>3093000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2954000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>3070000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>3082000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>3191000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>3054000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2976000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2876000</v>
       </c>
     </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
@@ -2141,18 +2245,18 @@
       <c r="G47" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="H47" s="3">
-        <v>2000</v>
+      <c r="H47" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="I47" s="3">
         <v>2000</v>
       </c>
       <c r="J47" s="3">
+        <v>2000</v>
+      </c>
+      <c r="K47" s="3">
         <v>11000</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
-      </c>
       <c r="L47" s="3">
         <v>0</v>
       </c>
@@ -2165,90 +2269,99 @@
       <c r="O47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
+        <v>421000</v>
+      </c>
+      <c r="E48" s="3">
         <v>429000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>438000</v>
-      </c>
-      <c r="F48" s="3">
-        <v>448000</v>
       </c>
       <c r="G48" s="3">
         <v>448000</v>
       </c>
       <c r="H48" s="3">
+        <v>438000</v>
+      </c>
+      <c r="I48" s="3">
         <v>1029000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1030000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1034000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>499000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>997000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1039000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1075000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1122000</v>
       </c>
     </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
+        <v>1912000</v>
+      </c>
+      <c r="E49" s="3">
         <v>1934000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2785000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2803000</v>
       </c>
-      <c r="G49" s="3">
-        <v>2817000</v>
-      </c>
       <c r="H49" s="3">
+        <v>1959000</v>
+      </c>
+      <c r="I49" s="3">
         <v>6119000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>6181000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>5647000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2480000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>5756000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>5825000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>5879000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>5835000</v>
       </c>
     </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -2288,8 +2401,11 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -2329,49 +2445,55 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
+        <v>259000</v>
+      </c>
+      <c r="E52" s="3">
         <v>261000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>252000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>283000</v>
       </c>
-      <c r="G52" s="3">
-        <v>280000</v>
-      </c>
       <c r="H52" s="3">
+        <v>1148000</v>
+      </c>
+      <c r="I52" s="3">
         <v>2550000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>523000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1085000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>6342000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1839000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1838000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1785000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1808000</v>
       </c>
     </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -2411,49 +2533,55 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
+        <v>4452000</v>
+      </c>
+      <c r="E54" s="3">
         <v>4674000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>4783000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>5007000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>4990000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>13223000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>11279000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>11442000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>11507000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>11783000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>11756000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>11715000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>11641000</v>
       </c>
     </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -2469,8 +2597,9 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -2486,254 +2615,273 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
+        <v>332000</v>
+      </c>
+      <c r="E57" s="3">
         <v>400000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>478000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>482000</v>
       </c>
-      <c r="G57" s="3">
-        <v>505000</v>
-      </c>
       <c r="H57" s="3">
+        <v>440000</v>
+      </c>
+      <c r="I57" s="3">
         <v>820000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>832000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>952000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>594000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>876000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>949000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>901000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>826000</v>
       </c>
     </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>51000</v>
       </c>
       <c r="E58" s="3">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="F58" s="3">
         <v>15000</v>
       </c>
       <c r="G58" s="3">
-        <v>67000</v>
+        <v>15000</v>
       </c>
       <c r="H58" s="3">
+        <v>63000</v>
+      </c>
+      <c r="I58" s="3">
         <v>113000</v>
-      </c>
-      <c r="I58" s="3">
-        <v>105000</v>
       </c>
       <c r="J58" s="3">
         <v>105000</v>
       </c>
       <c r="K58" s="3">
+        <v>105000</v>
+      </c>
+      <c r="L58" s="3">
         <v>110000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>106000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>108000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>83000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>73000</v>
       </c>
     </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
+        <v>933000</v>
+      </c>
+      <c r="E59" s="3">
         <v>1008000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>668000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>738000</v>
       </c>
-      <c r="G59" s="3">
-        <v>612000</v>
-      </c>
       <c r="H59" s="3">
+        <v>704000</v>
+      </c>
+      <c r="I59" s="3">
         <v>1429000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1512000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1536000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2682000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1788000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1776000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1846000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1909000</v>
       </c>
     </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
+        <v>1420000</v>
+      </c>
+      <c r="E60" s="3">
         <v>1527000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1254000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1335000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1333000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2680000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2657000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2816000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2713000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2770000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2833000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2830000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2808000</v>
       </c>
     </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
+        <v>1349000</v>
+      </c>
+      <c r="E61" s="3">
         <v>1351000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2847000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2917000</v>
       </c>
-      <c r="G61" s="3">
-        <v>2824000</v>
-      </c>
       <c r="H61" s="3">
+        <v>2821000</v>
+      </c>
+      <c r="I61" s="3">
         <v>7743000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>5660000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>5746000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>5555000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>5611000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>5497000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>5516000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>5518000</v>
       </c>
     </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
+        <v>278000</v>
+      </c>
+      <c r="E62" s="3">
         <v>293000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>276000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>292000</v>
       </c>
-      <c r="G62" s="3">
-        <v>303000</v>
-      </c>
       <c r="H62" s="3">
+        <v>320000</v>
+      </c>
+      <c r="I62" s="3">
         <v>360000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>373000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>364000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1485000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1681000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1778000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1770000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1782000</v>
       </c>
     </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -2773,8 +2921,11 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -2814,8 +2965,11 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -2855,49 +3009,55 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
+        <v>3245000</v>
+      </c>
+      <c r="E66" s="3">
         <v>3387000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4594000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4767000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4689000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>11576000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>9450000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>9679000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>9752000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>10063000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>10111000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>10118000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>10111000</v>
       </c>
     </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -2913,8 +3073,9 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -2954,8 +3115,11 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -2995,8 +3159,11 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -3013,7 +3180,7 @@
         <v>276000</v>
       </c>
       <c r="H70" s="3">
-        <v>275000</v>
+        <v>276000</v>
       </c>
       <c r="I70" s="3">
         <v>275000</v>
@@ -3031,13 +3198,16 @@
         <v>275000</v>
       </c>
       <c r="N70" s="3">
-        <v>274000</v>
+        <v>275000</v>
       </c>
       <c r="O70" s="3">
         <v>274000</v>
       </c>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>274000</v>
+      </c>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -3077,49 +3247,55 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
+        <v>535000</v>
+      </c>
+      <c r="E72" s="3">
         <v>561000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-517000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-463000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-421000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>967000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1095000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1080000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1075000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1095000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1030000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>993000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1031000</v>
       </c>
     </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -3159,8 +3335,11 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -3200,8 +3379,11 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -3241,49 +3423,55 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
+        <v>933000</v>
+      </c>
+      <c r="E76" s="3">
         <v>1013000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-85000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-34000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>25000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1372000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1555000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1489000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1480000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1445000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1370000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1323000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1256000</v>
       </c>
     </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -3323,95 +3511,104 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
     </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="E81" s="3">
         <v>1082000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-73000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-40000</v>
       </c>
-      <c r="G81" s="3">
-        <v>-327000</v>
-      </c>
       <c r="H81" s="3">
+        <v>-318000</v>
+      </c>
+      <c r="I81" s="3">
         <v>-129000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>17000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>7000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>46000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>65000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>37000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-38000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>60000</v>
       </c>
     </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -3427,49 +3624,53 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D83" s="3">
+        <v>-38000</v>
+      </c>
+      <c r="E83" s="3">
         <v>155000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>137000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>134000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>-10000</v>
       </c>
-      <c r="H83" s="3" t="s">
+      <c r="I83" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>107000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>106000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>610000</v>
-      </c>
-      <c r="L83" s="3">
-        <v>152000</v>
       </c>
       <c r="M83" s="3">
         <v>152000</v>
       </c>
       <c r="N83" s="3">
+        <v>152000</v>
+      </c>
+      <c r="O83" s="3">
         <v>147000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>153000</v>
       </c>
     </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -3509,8 +3710,11 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -3550,8 +3754,11 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -3591,8 +3798,11 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -3632,8 +3842,11 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -3673,49 +3886,55 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
+        <v>-170000</v>
+      </c>
+      <c r="E89" s="3">
         <v>11000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>62000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-35000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-33000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>189000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>227000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>311000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>427000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>126000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>84000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>34000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>252000</v>
       </c>
     </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -3731,49 +3950,53 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D91" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-13000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-8000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-18000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-42000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-51000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-19000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-88000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-115000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-94000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-80000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-106000</v>
       </c>
     </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -3813,8 +4036,11 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -3854,49 +4080,55 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
+        <v>172000</v>
+      </c>
+      <c r="E94" s="3">
         <v>2098000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-27000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-54000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>15000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-111000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-108000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-86000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-387000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-121000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-91000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-86000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-114000</v>
       </c>
     </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -3912,8 +4144,9 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
@@ -3938,8 +4171,8 @@
       <c r="J96" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -3953,8 +4186,11 @@
       <c r="O96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -3994,8 +4230,11 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -4035,8 +4274,11 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -4076,127 +4318,139 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D100" s="3">
+        <v>-64000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1511000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-65000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>80000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-2718000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>2145000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-91000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-175000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>100000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-8000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>1000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-18000</v>
       </c>
     </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D101" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-20000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>2000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-10000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-7000</v>
       </c>
-      <c r="H101" s="3" t="s">
+      <c r="I101" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-13000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-6000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-50000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-24000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-13000</v>
-      </c>
-      <c r="N101" s="3">
-        <v>-6000</v>
       </c>
       <c r="O101" s="3">
         <v>-6000</v>
       </c>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P101" s="3">
+        <v>-6000</v>
+      </c>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
+        <v>-67000</v>
+      </c>
+      <c r="E102" s="3">
         <v>593000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-37000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-16000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-2728000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>2203000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>30000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>40000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-9000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>81000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-28000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-57000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>114000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/VYX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VYX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="92">
   <si>
     <t>VYX</t>
   </si>
@@ -656,212 +656,225 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>617000</v>
+      </c>
+      <c r="E8" s="3">
         <v>682000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>711000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>575000</v>
       </c>
-      <c r="G8" s="3">
-        <v>858000</v>
-      </c>
       <c r="H8" s="3">
+        <v>710000</v>
+      </c>
+      <c r="I8" s="3">
         <v>796000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>809000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>667000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>906000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3793000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1972000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1997000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1866000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2034000</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>480000</v>
+      </c>
+      <c r="E9" s="3">
         <v>518000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>545000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>491000</v>
       </c>
-      <c r="G9" s="3">
-        <v>652000</v>
-      </c>
       <c r="H9" s="3">
+        <v>564000</v>
+      </c>
+      <c r="I9" s="3">
         <v>642000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>611000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>523000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>682000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2815000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1481000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1526000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1455000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1531000</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>137000</v>
+      </c>
+      <c r="E10" s="3">
         <v>164000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>166000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>84000</v>
       </c>
-      <c r="G10" s="3">
-        <v>206000</v>
-      </c>
       <c r="H10" s="3">
+        <v>146000</v>
+      </c>
+      <c r="I10" s="3">
         <v>154000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>198000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>144000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>224000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>978000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>491000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>471000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>411000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>503000</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -878,52 +891,56 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>37000</v>
+      </c>
+      <c r="E12" s="3">
         <v>29000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>34000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>30000</v>
       </c>
-      <c r="G12" s="3">
-        <v>54000</v>
-      </c>
       <c r="H12" s="3">
+        <v>41000</v>
+      </c>
+      <c r="I12" s="3">
         <v>30000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>29000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>20000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>49000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>127000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>39000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>51000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>64000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>63000</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -966,96 +983,105 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>32000</v>
+      </c>
+      <c r="E14" s="3">
         <v>28000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>2000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>29000</v>
       </c>
-      <c r="G14" s="3">
-        <v>34000</v>
-      </c>
       <c r="H14" s="3">
+        <v>43000</v>
+      </c>
+      <c r="I14" s="3">
         <v>121000</v>
-      </c>
-      <c r="I14" s="3">
-        <v>28000</v>
       </c>
       <c r="J14" s="3">
         <v>28000</v>
       </c>
       <c r="K14" s="3">
+        <v>28000</v>
+      </c>
+      <c r="L14" s="3">
         <v>7000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>62000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>9000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>35000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>31000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>23000</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>60000</v>
+      </c>
+      <c r="E15" s="3">
         <v>39500</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>70000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>86000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>81000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>105800</v>
-      </c>
-      <c r="I15" s="3">
-        <v>155000</v>
       </c>
       <c r="J15" s="3">
         <v>155000</v>
       </c>
       <c r="K15" s="3">
+        <v>155000</v>
+      </c>
+      <c r="L15" s="3">
         <v>151000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>30000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>17000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>18000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>22000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>23000</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1069,96 +1095,103 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>606000</v>
+      </c>
+      <c r="E17" s="3">
         <v>640000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>687000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>606000</v>
       </c>
-      <c r="G17" s="3">
-        <v>820000</v>
-      </c>
       <c r="H17" s="3">
+        <v>702000</v>
+      </c>
+      <c r="I17" s="3">
         <v>888000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>758000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>651000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>880000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3657000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1785000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1894000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1833000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1911000</v>
       </c>
     </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>11000</v>
+      </c>
+      <c r="E18" s="3">
         <v>42000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>24000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-31000</v>
       </c>
-      <c r="G18" s="3">
-        <v>38000</v>
-      </c>
       <c r="H18" s="3">
+        <v>8000</v>
+      </c>
+      <c r="I18" s="3">
         <v>-92000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>51000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>16000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>26000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>136000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>187000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>103000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>33000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>123000</v>
       </c>
     </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1175,228 +1208,244 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E20" s="3">
         <v>12000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>16000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>5000</v>
       </c>
-      <c r="G20" s="3">
-        <v>21000</v>
-      </c>
       <c r="H20" s="3">
+        <v>4000</v>
+      </c>
+      <c r="I20" s="3">
         <v>39000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>24000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>11000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>6000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>99000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-1000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>1000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>9000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>113000</v>
       </c>
     </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>74000</v>
+      </c>
+      <c r="E21" s="3">
         <v>69500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>78000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>50000</v>
       </c>
-      <c r="G21" s="3">
-        <v>98000</v>
-      </c>
       <c r="H21" s="3">
+        <v>85000</v>
+      </c>
+      <c r="I21" s="3">
         <v>-25300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>182000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>160000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>171000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>845000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>338000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>256000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>189000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>389000</v>
       </c>
     </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>15000</v>
+      </c>
+      <c r="E22" s="3">
         <v>14000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>40000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>41000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>39000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>37000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>83000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>91000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>83000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>366000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>74000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>67000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>63000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>64000</v>
       </c>
     </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>-27000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-8000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-32000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-105000</v>
       </c>
-      <c r="G23" s="3">
-        <v>-54000</v>
-      </c>
       <c r="H23" s="3">
+        <v>-76000</v>
+      </c>
+      <c r="I23" s="3">
         <v>-288000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-79000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-111000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-67000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-131000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>112000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>37000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-21000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>172000</v>
       </c>
     </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="E24" s="3">
         <v>1000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-1000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>18000</v>
       </c>
-      <c r="G24" s="3">
-        <v>-14000</v>
-      </c>
       <c r="H24" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="I24" s="3">
         <v>-16000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>187000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>8000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>5000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>72000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>43000</v>
       </c>
-      <c r="N24" s="3">
-        <v>0</v>
-      </c>
       <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3">
         <v>13000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>109000</v>
       </c>
     </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1439,96 +1488,105 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>-20000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-9000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-31000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-123000</v>
       </c>
-      <c r="G26" s="3">
-        <v>-40000</v>
-      </c>
       <c r="H26" s="3">
+        <v>-71000</v>
+      </c>
+      <c r="I26" s="3">
         <v>-272000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-266000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-119000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-72000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-203000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>69000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>37000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-34000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>63000</v>
       </c>
     </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>-21000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-14000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1078000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-77000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-44000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-322000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-133000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>13000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>3000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-217000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>65000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>31000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-37000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>60000</v>
       </c>
     </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -1571,52 +1629,58 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D29" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E29" s="3">
         <v>-2000</v>
       </c>
-      <c r="E29" s="3">
+      <c r="F29" s="3">
         <v>1113000</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>50000</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
+        <v>30000</v>
+      </c>
+      <c r="I29" s="3">
+        <v>-47000</v>
+      </c>
+      <c r="J29" s="3">
+        <v>138000</v>
+      </c>
+      <c r="K29" s="3">
+        <v>136000</v>
+      </c>
+      <c r="L29" s="3">
+        <v>79000</v>
+      </c>
+      <c r="M29" s="3">
+        <v>263000</v>
+      </c>
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3">
+        <v>6000</v>
+      </c>
+      <c r="P29" s="3">
         <v>-1000</v>
       </c>
-      <c r="H29" s="3">
-        <v>-47000</v>
-      </c>
-      <c r="I29" s="3">
-        <v>138000</v>
-      </c>
-      <c r="J29" s="3">
-        <v>136000</v>
-      </c>
-      <c r="K29" s="3">
-        <v>79000</v>
-      </c>
-      <c r="L29" s="3">
-        <v>263000</v>
-      </c>
-      <c r="M29" s="3">
-        <v>0</v>
-      </c>
-      <c r="N29" s="3">
-        <v>6000</v>
-      </c>
-      <c r="O29" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="P29" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -1659,8 +1723,11 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -1703,96 +1770,105 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-12000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-16000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-5000</v>
       </c>
-      <c r="G32" s="3">
-        <v>-21000</v>
-      </c>
       <c r="H32" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="I32" s="3">
         <v>-39000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-24000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-11000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-6000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-99000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>1000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-1000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-9000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-113000</v>
       </c>
     </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
+        <v>-17000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-11000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1082000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-73000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-40000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-318000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-129000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>17000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>7000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>46000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>65000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>37000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-38000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>60000</v>
       </c>
     </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -1835,101 +1911,110 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
+        <v>-17000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-11000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1082000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-73000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-40000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-318000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-129000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>17000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>7000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>46000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>65000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>37000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-38000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>60000</v>
       </c>
     </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
     </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -1946,8 +2031,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -1964,52 +2050,56 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>573000</v>
+      </c>
+      <c r="E41" s="3">
         <v>724000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>795000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>204000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>246000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>259000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>675000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>547000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>519000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>221000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>434000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>398000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>412000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>447000</v>
       </c>
     </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
@@ -2029,17 +2119,17 @@
         <v>0</v>
       </c>
       <c r="I42" s="3">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="J42" s="3">
         <v>20000</v>
       </c>
       <c r="K42" s="3">
+        <v>20000</v>
+      </c>
+      <c r="L42" s="3">
         <v>33000</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
       <c r="M42" s="3">
         <v>0</v>
       </c>
@@ -2052,96 +2142,105 @@
       <c r="P42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
+        <v>567000</v>
+      </c>
+      <c r="E43" s="3">
         <v>539000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>623000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>429000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>484000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>414000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>950000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>986000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1009000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>550000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1116000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1085000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1071000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>959000</v>
       </c>
     </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
-        <v>208000</v>
+        <v>218000</v>
       </c>
       <c r="E44" s="3">
         <v>208000</v>
       </c>
       <c r="F44" s="3">
+        <v>208000</v>
+      </c>
+      <c r="G44" s="3">
         <v>220000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>259000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>250000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>725000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>709000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>792000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>357000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>827000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>858000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>805000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>754000</v>
       </c>
     </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
@@ -2151,85 +2250,91 @@
       <c r="E45" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="F45" s="3">
+      <c r="F45" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="G45" s="3">
         <v>1000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>5000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>89000</v>
-      </c>
-      <c r="I45" s="3">
-        <v>1000</v>
       </c>
       <c r="J45" s="3">
         <v>1000</v>
       </c>
       <c r="K45" s="3">
+        <v>1000</v>
+      </c>
+      <c r="L45" s="3">
         <v>460000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1954000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>814000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>713000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>688000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>716000</v>
       </c>
     </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
+        <v>1569000</v>
+      </c>
+      <c r="E46" s="3">
         <v>1671000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1825000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1064000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1238000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1206000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>3093000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2954000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>3070000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>3082000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>3191000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>3054000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2976000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2876000</v>
       </c>
     </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
@@ -2248,18 +2353,18 @@
       <c r="H47" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="I47" s="3">
-        <v>2000</v>
+      <c r="I47" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="J47" s="3">
         <v>2000</v>
       </c>
       <c r="K47" s="3">
+        <v>2000</v>
+      </c>
+      <c r="L47" s="3">
         <v>11000</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
-      </c>
       <c r="M47" s="3">
         <v>0</v>
       </c>
@@ -2272,96 +2377,105 @@
       <c r="P47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
+        <v>409000</v>
+      </c>
+      <c r="E48" s="3">
         <v>421000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>429000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>438000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>448000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>438000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1029000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1030000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1034000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>499000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>997000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1039000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1075000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1122000</v>
       </c>
     </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
+        <v>1900000</v>
+      </c>
+      <c r="E49" s="3">
         <v>1912000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1934000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2785000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2803000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1959000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>6119000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>6181000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>5647000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2480000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>5756000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>5825000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>5879000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>5835000</v>
       </c>
     </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -2404,8 +2518,11 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -2448,52 +2565,58 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
+        <v>262000</v>
+      </c>
+      <c r="E52" s="3">
         <v>259000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>261000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>252000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>283000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1148000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2550000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>523000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1085000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>6342000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1839000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1838000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1785000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1808000</v>
       </c>
     </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -2536,52 +2659,58 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
+        <v>4336000</v>
+      </c>
+      <c r="E54" s="3">
         <v>4452000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>4674000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>4783000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>5007000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>4990000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>13223000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>11279000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>11442000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>11507000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>11783000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>11756000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>11715000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>11641000</v>
       </c>
     </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -2598,8 +2727,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -2616,272 +2746,291 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
+        <v>325000</v>
+      </c>
+      <c r="E57" s="3">
         <v>332000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>400000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>478000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>482000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>440000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>820000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>832000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>952000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>594000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>876000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>949000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>901000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>826000</v>
       </c>
     </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
+        <v>0</v>
+      </c>
+      <c r="E58" s="3">
         <v>51000</v>
       </c>
-      <c r="E58" s="3">
-        <v>0</v>
-      </c>
       <c r="F58" s="3">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="G58" s="3">
         <v>15000</v>
       </c>
       <c r="H58" s="3">
+        <v>15000</v>
+      </c>
+      <c r="I58" s="3">
         <v>63000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>113000</v>
-      </c>
-      <c r="J58" s="3">
-        <v>105000</v>
       </c>
       <c r="K58" s="3">
         <v>105000</v>
       </c>
       <c r="L58" s="3">
+        <v>105000</v>
+      </c>
+      <c r="M58" s="3">
         <v>110000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>106000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>108000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>83000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>73000</v>
       </c>
     </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
+        <v>988000</v>
+      </c>
+      <c r="E59" s="3">
         <v>933000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1008000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>668000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>738000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>704000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1429000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1512000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1536000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2682000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1788000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1776000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1846000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1909000</v>
       </c>
     </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
+        <v>1406000</v>
+      </c>
+      <c r="E60" s="3">
         <v>1420000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1527000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1254000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1335000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1333000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2680000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2657000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2816000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2713000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2770000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2833000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2830000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2808000</v>
       </c>
     </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
+        <v>1340000</v>
+      </c>
+      <c r="E61" s="3">
         <v>1349000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1351000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2847000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2917000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2821000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>7743000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>5660000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>5746000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>5555000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>5611000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>5497000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>5516000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>5518000</v>
       </c>
     </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
+        <v>253000</v>
+      </c>
+      <c r="E62" s="3">
         <v>278000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>293000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>276000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>292000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>320000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>360000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>373000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>364000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1485000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1681000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1778000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1770000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1782000</v>
       </c>
     </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -2924,8 +3073,11 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -2968,8 +3120,11 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -3012,52 +3167,58 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
+        <v>3203000</v>
+      </c>
+      <c r="E66" s="3">
         <v>3245000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3387000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4594000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4767000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>4689000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>11576000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>9450000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>9679000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>9752000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>10063000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>10111000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>10118000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>10111000</v>
       </c>
     </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -3074,8 +3235,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -3118,8 +3280,11 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -3162,8 +3327,11 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -3183,7 +3351,7 @@
         <v>276000</v>
       </c>
       <c r="I70" s="3">
-        <v>275000</v>
+        <v>276000</v>
       </c>
       <c r="J70" s="3">
         <v>275000</v>
@@ -3201,13 +3369,16 @@
         <v>275000</v>
       </c>
       <c r="O70" s="3">
-        <v>274000</v>
+        <v>275000</v>
       </c>
       <c r="P70" s="3">
         <v>274000</v>
       </c>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>274000</v>
+      </c>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -3250,52 +3421,58 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
+        <v>496000</v>
+      </c>
+      <c r="E72" s="3">
         <v>535000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>561000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-517000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-463000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-421000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>967000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1095000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1080000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1075000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1095000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1030000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>993000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>1031000</v>
       </c>
     </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -3338,8 +3515,11 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -3382,8 +3562,11 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -3426,52 +3609,58 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
+        <v>857000</v>
+      </c>
+      <c r="E76" s="3">
         <v>933000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1013000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-85000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-34000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>25000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1372000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1555000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1489000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1480000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1445000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1370000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1323000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1256000</v>
       </c>
     </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -3514,101 +3703,110 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
     </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
+        <v>-17000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-11000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1082000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-73000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-40000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-318000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-129000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>17000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>7000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>46000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>65000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>37000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-38000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>60000</v>
       </c>
     </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -3625,52 +3823,56 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D83" s="3">
+        <v>74000</v>
+      </c>
+      <c r="E83" s="3">
         <v>-38000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>155000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>137000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>134000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>-10000</v>
       </c>
-      <c r="I83" s="3" t="s">
+      <c r="J83" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>107000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>106000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>610000</v>
-      </c>
-      <c r="M83" s="3">
-        <v>152000</v>
       </c>
       <c r="N83" s="3">
         <v>152000</v>
       </c>
       <c r="O83" s="3">
+        <v>152000</v>
+      </c>
+      <c r="P83" s="3">
         <v>147000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>153000</v>
       </c>
     </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -3713,8 +3915,11 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -3757,8 +3962,11 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -3801,8 +4009,11 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -3845,8 +4056,11 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -3889,52 +4103,58 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
+        <v>-42000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-170000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>11000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>62000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-35000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-33000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>189000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>227000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>311000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>427000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>126000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>84000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>34000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>252000</v>
       </c>
     </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -3951,52 +4171,56 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D91" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-7000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-13000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-8000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-18000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-42000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-51000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-19000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-88000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-115000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-94000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-80000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-106000</v>
       </c>
     </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -4039,8 +4263,11 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -4083,52 +4310,58 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
+        <v>-35000</v>
+      </c>
+      <c r="E94" s="3">
         <v>172000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>2098000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-27000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-54000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>15000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-111000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-108000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-86000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-387000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-121000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-91000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-86000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-114000</v>
       </c>
     </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -4145,8 +4378,9 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
@@ -4174,8 +4408,8 @@
       <c r="K96" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -4189,8 +4423,11 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -4233,8 +4470,11 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -4277,8 +4517,11 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -4321,136 +4564,148 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D100" s="3">
+        <v>-74000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-64000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1511000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-65000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>80000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-2718000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>2145000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-91000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-175000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>100000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-8000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>1000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-18000</v>
       </c>
     </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D101" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="E101" s="3">
         <v>8000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-20000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>2000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-10000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-7000</v>
       </c>
-      <c r="I101" s="3" t="s">
+      <c r="J101" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-13000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-6000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-50000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-24000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-13000</v>
-      </c>
-      <c r="O101" s="3">
-        <v>-6000</v>
       </c>
       <c r="P101" s="3">
         <v>-6000</v>
       </c>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3">
+        <v>-6000</v>
+      </c>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
+        <v>-150000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-67000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>593000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-37000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-16000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-2728000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>2203000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>30000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>40000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-9000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>81000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-28000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-57000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>114000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/VYX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VYX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="92">
   <si>
     <t>VYX</t>
   </si>
@@ -656,225 +656,238 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>666000</v>
+      </c>
+      <c r="E8" s="3">
         <v>617000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>682000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>711000</v>
       </c>
-      <c r="G8" s="3">
-        <v>575000</v>
-      </c>
       <c r="H8" s="3">
+        <v>722000</v>
+      </c>
+      <c r="I8" s="3">
         <v>710000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>796000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>809000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>667000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>906000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3793000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1972000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1997000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1866000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2034000</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>509000</v>
+      </c>
+      <c r="E9" s="3">
         <v>480000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>518000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>545000</v>
       </c>
-      <c r="G9" s="3">
-        <v>491000</v>
-      </c>
       <c r="H9" s="3">
+        <v>577000</v>
+      </c>
+      <c r="I9" s="3">
         <v>564000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>642000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>611000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>523000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>682000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2815000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1481000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1526000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1455000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1531000</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>157000</v>
+      </c>
+      <c r="E10" s="3">
         <v>137000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>164000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>166000</v>
       </c>
-      <c r="G10" s="3">
-        <v>84000</v>
-      </c>
       <c r="H10" s="3">
+        <v>145000</v>
+      </c>
+      <c r="I10" s="3">
         <v>146000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>154000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>198000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>144000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>224000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>978000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>491000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>471000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>411000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>503000</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -892,55 +905,59 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>30000</v>
+      </c>
+      <c r="E12" s="3">
         <v>37000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>29000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>34000</v>
-      </c>
-      <c r="G12" s="3">
-        <v>30000</v>
       </c>
       <c r="H12" s="3">
         <v>41000</v>
       </c>
       <c r="I12" s="3">
+        <v>41000</v>
+      </c>
+      <c r="J12" s="3">
         <v>30000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>29000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>20000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>49000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>127000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>39000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>51000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>64000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>63000</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -986,102 +1003,111 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>20000</v>
+      </c>
+      <c r="E14" s="3">
         <v>32000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>28000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>2000</v>
       </c>
-      <c r="G14" s="3">
-        <v>29000</v>
-      </c>
       <c r="H14" s="3">
+        <v>45000</v>
+      </c>
+      <c r="I14" s="3">
         <v>43000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>121000</v>
-      </c>
-      <c r="J14" s="3">
-        <v>28000</v>
       </c>
       <c r="K14" s="3">
         <v>28000</v>
       </c>
       <c r="L14" s="3">
+        <v>28000</v>
+      </c>
+      <c r="M14" s="3">
         <v>7000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>62000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>9000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>35000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>31000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>23000</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>58000</v>
+      </c>
+      <c r="E15" s="3">
         <v>60000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>39500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>70000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>86000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>81000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>105800</v>
-      </c>
-      <c r="J15" s="3">
-        <v>155000</v>
       </c>
       <c r="K15" s="3">
         <v>155000</v>
       </c>
       <c r="L15" s="3">
+        <v>155000</v>
+      </c>
+      <c r="M15" s="3">
         <v>151000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>30000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>17000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>18000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>22000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>23000</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1096,102 +1122,109 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>633000</v>
+      </c>
+      <c r="E17" s="3">
         <v>606000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>640000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>687000</v>
       </c>
-      <c r="G17" s="3">
-        <v>606000</v>
-      </c>
       <c r="H17" s="3">
+        <v>712000</v>
+      </c>
+      <c r="I17" s="3">
         <v>702000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>888000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>758000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>651000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>880000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3657000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1785000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1894000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1833000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1911000</v>
       </c>
     </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>33000</v>
+      </c>
+      <c r="E18" s="3">
         <v>11000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>42000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>24000</v>
       </c>
-      <c r="G18" s="3">
-        <v>-31000</v>
-      </c>
       <c r="H18" s="3">
+        <v>10000</v>
+      </c>
+      <c r="I18" s="3">
         <v>8000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-92000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>51000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>16000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>26000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>136000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>187000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>103000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>33000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>123000</v>
       </c>
     </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1209,243 +1242,259 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-3000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>12000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>16000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>5000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>4000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>39000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>24000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>11000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>6000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>99000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-1000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>1000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>9000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>113000</v>
       </c>
     </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>88000</v>
+      </c>
+      <c r="E21" s="3">
         <v>74000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>69500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>78000</v>
       </c>
-      <c r="G21" s="3">
-        <v>50000</v>
-      </c>
       <c r="H21" s="3">
+        <v>91000</v>
+      </c>
+      <c r="I21" s="3">
         <v>85000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-25300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>182000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>160000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>171000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>845000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>338000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>256000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>189000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>389000</v>
       </c>
     </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>14000</v>
+      </c>
+      <c r="E22" s="3">
         <v>15000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>14000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>40000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>41000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>39000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>37000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>83000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>91000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>83000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>366000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>74000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>67000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>63000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>64000</v>
       </c>
     </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-27000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-8000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-32000</v>
       </c>
-      <c r="G23" s="3">
-        <v>-105000</v>
-      </c>
       <c r="H23" s="3">
+        <v>-80000</v>
+      </c>
+      <c r="I23" s="3">
         <v>-76000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-288000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-79000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-111000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-67000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-131000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>112000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>37000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-21000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>172000</v>
       </c>
     </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="E24" s="3">
         <v>-7000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-1000</v>
       </c>
-      <c r="G24" s="3">
-        <v>18000</v>
-      </c>
       <c r="H24" s="3">
+        <v>10000</v>
+      </c>
+      <c r="I24" s="3">
         <v>-5000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-16000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>187000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>8000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>5000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>72000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>43000</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
       <c r="P24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3">
         <v>13000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>109000</v>
       </c>
     </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1491,102 +1540,111 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-20000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-9000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-31000</v>
       </c>
-      <c r="G26" s="3">
-        <v>-123000</v>
-      </c>
       <c r="H26" s="3">
+        <v>-90000</v>
+      </c>
+      <c r="I26" s="3">
         <v>-71000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-272000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-266000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-119000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-72000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-203000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>69000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>37000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-34000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>63000</v>
       </c>
     </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-21000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-14000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1078000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-77000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-44000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-322000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-133000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>13000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>3000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-217000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>65000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>31000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-37000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>60000</v>
       </c>
     </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -1632,55 +1690,61 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D29" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E29" s="3">
         <v>3000</v>
       </c>
-      <c r="E29" s="3">
+      <c r="F29" s="3">
         <v>-2000</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>1113000</v>
       </c>
-      <c r="G29" s="3">
-        <v>50000</v>
-      </c>
       <c r="H29" s="3">
-        <v>30000</v>
+        <v>17000</v>
       </c>
       <c r="I29" s="3">
+        <v>31000</v>
+      </c>
+      <c r="J29" s="3">
         <v>-47000</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>138000</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>136000</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>79000</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>263000</v>
       </c>
-      <c r="N29" s="3">
-        <v>0</v>
-      </c>
       <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3">
         <v>6000</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q29" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -1726,8 +1790,11 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -1773,102 +1840,111 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E32" s="3">
         <v>3000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-12000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-16000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-5000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-4000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-39000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-24000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-11000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-6000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-99000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>1000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-1000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-9000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-113000</v>
       </c>
     </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
+        <v>0</v>
+      </c>
+      <c r="E33" s="3">
         <v>-17000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-11000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1082000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-73000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-40000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-318000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-129000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>17000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>7000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>46000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>65000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>37000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-38000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>60000</v>
       </c>
     </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -1914,107 +1990,116 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
+        <v>0</v>
+      </c>
+      <c r="E35" s="3">
         <v>-17000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-11000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1082000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-73000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-40000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-318000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-129000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>17000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>7000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>46000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>65000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>37000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-38000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>60000</v>
       </c>
     </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
     </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -2032,8 +2117,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -2051,55 +2137,59 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>276000</v>
+      </c>
+      <c r="E41" s="3">
         <v>573000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>724000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>795000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>204000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>246000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>259000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>675000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>547000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>519000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>221000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>434000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>398000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>412000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>447000</v>
       </c>
     </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
@@ -2122,17 +2212,17 @@
         <v>0</v>
       </c>
       <c r="J42" s="3">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="K42" s="3">
         <v>20000</v>
       </c>
       <c r="L42" s="3">
+        <v>20000</v>
+      </c>
+      <c r="M42" s="3">
         <v>33000</v>
       </c>
-      <c r="M42" s="3">
-        <v>0</v>
-      </c>
       <c r="N42" s="3">
         <v>0</v>
       </c>
@@ -2145,102 +2235,111 @@
       <c r="Q42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
+        <v>507000</v>
+      </c>
+      <c r="E43" s="3">
         <v>567000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>539000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>623000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>429000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>484000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>414000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>950000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>986000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1009000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>550000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1116000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1085000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1071000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>959000</v>
       </c>
     </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
+        <v>212000</v>
+      </c>
+      <c r="E44" s="3">
         <v>218000</v>
-      </c>
-      <c r="E44" s="3">
-        <v>208000</v>
       </c>
       <c r="F44" s="3">
         <v>208000</v>
       </c>
       <c r="G44" s="3">
+        <v>208000</v>
+      </c>
+      <c r="H44" s="3">
         <v>220000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>259000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>250000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>725000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>709000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>792000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>357000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>827000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>858000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>805000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>754000</v>
       </c>
     </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
@@ -2253,88 +2352,94 @@
       <c r="F45" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="G45" s="3">
+      <c r="G45" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="H45" s="3">
         <v>1000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>5000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>89000</v>
-      </c>
-      <c r="J45" s="3">
-        <v>1000</v>
       </c>
       <c r="K45" s="3">
         <v>1000</v>
       </c>
       <c r="L45" s="3">
+        <v>1000</v>
+      </c>
+      <c r="M45" s="3">
         <v>460000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1954000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>814000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>713000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>688000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>716000</v>
       </c>
     </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
+        <v>1222000</v>
+      </c>
+      <c r="E46" s="3">
         <v>1569000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1671000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1825000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1064000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1238000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1206000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>3093000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2954000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>3070000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>3082000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>3191000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>3054000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2976000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>2876000</v>
       </c>
     </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
@@ -2356,18 +2461,18 @@
       <c r="I47" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="J47" s="3">
-        <v>2000</v>
+      <c r="J47" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="K47" s="3">
         <v>2000</v>
       </c>
       <c r="L47" s="3">
+        <v>2000</v>
+      </c>
+      <c r="M47" s="3">
         <v>11000</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
-      </c>
       <c r="N47" s="3">
         <v>0</v>
       </c>
@@ -2380,102 +2485,111 @@
       <c r="Q47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
+        <v>398000</v>
+      </c>
+      <c r="E48" s="3">
         <v>409000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>421000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>429000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>438000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>448000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>438000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1029000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1030000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1034000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>499000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>997000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1039000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1075000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1122000</v>
       </c>
     </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
+        <v>1902000</v>
+      </c>
+      <c r="E49" s="3">
         <v>1900000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1912000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1934000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2785000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2803000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1959000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>6119000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>6181000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>5647000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>2480000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>5756000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>5825000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>5879000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>5835000</v>
       </c>
     </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -2521,8 +2635,11 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -2568,55 +2685,61 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
+        <v>270000</v>
+      </c>
+      <c r="E52" s="3">
         <v>262000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>259000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>261000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>252000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>283000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1148000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2550000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>523000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1085000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>6342000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1839000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1838000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1785000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1808000</v>
       </c>
     </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -2662,55 +2785,61 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
+        <v>3984000</v>
+      </c>
+      <c r="E54" s="3">
         <v>4336000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>4452000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>4674000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>4783000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>5007000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>4990000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>13223000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>11279000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>11442000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>11507000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>11783000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>11756000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>11715000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>11641000</v>
       </c>
     </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -2728,8 +2857,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -2747,55 +2877,59 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
+        <v>340000</v>
+      </c>
+      <c r="E57" s="3">
         <v>325000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>332000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>400000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>478000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>482000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>440000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>820000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>832000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>952000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>594000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>876000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>949000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>901000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>826000</v>
       </c>
     </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
@@ -2803,234 +2937,249 @@
         <v>0</v>
       </c>
       <c r="E58" s="3">
+        <v>0</v>
+      </c>
+      <c r="F58" s="3">
         <v>51000</v>
       </c>
-      <c r="F58" s="3">
-        <v>0</v>
-      </c>
       <c r="G58" s="3">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="H58" s="3">
         <v>15000</v>
       </c>
       <c r="I58" s="3">
+        <v>15000</v>
+      </c>
+      <c r="J58" s="3">
         <v>63000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>113000</v>
-      </c>
-      <c r="K58" s="3">
-        <v>105000</v>
       </c>
       <c r="L58" s="3">
         <v>105000</v>
       </c>
       <c r="M58" s="3">
+        <v>105000</v>
+      </c>
+      <c r="N58" s="3">
         <v>110000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>106000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>108000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>83000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>73000</v>
       </c>
     </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
+        <v>619000</v>
+      </c>
+      <c r="E59" s="3">
         <v>988000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>933000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1008000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>668000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>738000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>704000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1429000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1512000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1536000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2682000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1788000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1776000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1846000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1909000</v>
       </c>
     </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
+        <v>1054000</v>
+      </c>
+      <c r="E60" s="3">
         <v>1406000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1420000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1527000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1254000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1335000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1333000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2680000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2657000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2816000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2713000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2770000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2833000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2830000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2808000</v>
       </c>
     </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
+        <v>1337000</v>
+      </c>
+      <c r="E61" s="3">
         <v>1340000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1349000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1351000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2847000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2917000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2821000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>7743000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>5660000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>5746000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>5555000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>5611000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>5497000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>5516000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>5518000</v>
       </c>
     </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
+        <v>231000</v>
+      </c>
+      <c r="E62" s="3">
         <v>253000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>278000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>293000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>276000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>292000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>320000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>360000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>373000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>364000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1485000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1681000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1778000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1770000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1782000</v>
       </c>
     </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -3076,8 +3225,11 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -3123,8 +3275,11 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -3170,55 +3325,61 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
+        <v>2841000</v>
+      </c>
+      <c r="E66" s="3">
         <v>3203000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3245000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3387000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4594000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>4767000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>4689000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>11576000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>9450000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>9679000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>9752000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>10063000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>10111000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>10118000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>10111000</v>
       </c>
     </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -3236,8 +3397,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -3283,8 +3445,11 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -3330,8 +3495,11 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -3354,7 +3522,7 @@
         <v>276000</v>
       </c>
       <c r="J70" s="3">
-        <v>275000</v>
+        <v>276000</v>
       </c>
       <c r="K70" s="3">
         <v>275000</v>
@@ -3372,13 +3540,16 @@
         <v>275000</v>
       </c>
       <c r="P70" s="3">
-        <v>274000</v>
+        <v>275000</v>
       </c>
       <c r="Q70" s="3">
         <v>274000</v>
       </c>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>274000</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -3424,55 +3595,61 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
+        <v>492000</v>
+      </c>
+      <c r="E72" s="3">
         <v>496000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>535000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>561000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-517000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-463000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-421000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>967000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1095000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1080000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1075000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1095000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1030000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>993000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>1031000</v>
       </c>
     </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -3518,8 +3695,11 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -3565,8 +3745,11 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -3612,55 +3795,61 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
+        <v>867000</v>
+      </c>
+      <c r="E76" s="3">
         <v>857000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>933000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1013000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-85000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-34000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>25000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1372000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1555000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1489000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1480000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1445000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1370000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1323000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1256000</v>
       </c>
     </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -3706,107 +3895,116 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
     </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
+        <v>0</v>
+      </c>
+      <c r="E81" s="3">
         <v>-17000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-11000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1082000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-73000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-40000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-318000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-129000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>17000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>7000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>46000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>65000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>37000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-38000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>60000</v>
       </c>
     </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -3824,55 +4022,59 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D83" s="3">
+        <v>78000</v>
+      </c>
+      <c r="E83" s="3">
         <v>74000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>-38000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>155000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>137000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>134000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>-10000</v>
       </c>
-      <c r="J83" s="3" t="s">
+      <c r="K83" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>107000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>106000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>610000</v>
-      </c>
-      <c r="N83" s="3">
-        <v>152000</v>
       </c>
       <c r="O83" s="3">
         <v>152000</v>
       </c>
       <c r="P83" s="3">
+        <v>152000</v>
+      </c>
+      <c r="Q83" s="3">
         <v>147000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>153000</v>
       </c>
     </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -3918,8 +4120,11 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -3965,8 +4170,11 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -4012,8 +4220,11 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -4059,8 +4270,11 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -4106,55 +4320,61 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
+        <v>-242000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-42000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-170000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>11000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>62000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-35000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-33000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>189000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>227000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>311000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>427000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>126000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>84000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>34000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>252000</v>
       </c>
     </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -4172,55 +4392,59 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D91" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-8000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-7000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-2000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-13000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-8000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-18000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-42000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-51000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-19000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-88000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-115000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-94000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-80000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-106000</v>
       </c>
     </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -4266,8 +4490,11 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -4313,55 +4540,61 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
+        <v>-40000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-35000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>172000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>2098000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-27000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-54000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>15000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-111000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-108000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-86000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-387000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-121000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-91000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-86000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-114000</v>
       </c>
     </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -4379,8 +4612,9 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
@@ -4411,8 +4645,8 @@
       <c r="L96" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -4426,8 +4660,11 @@
       <c r="Q96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -4473,8 +4710,11 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -4520,8 +4760,11 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -4567,55 +4810,61 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D100" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-74000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-64000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1511000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-65000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>80000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-2718000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>2145000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-91000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-175000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>1000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>100000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-8000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-18000</v>
       </c>
     </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
@@ -4623,89 +4872,95 @@
         <v>-7000</v>
       </c>
       <c r="E101" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="F101" s="3">
         <v>8000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-20000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>2000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-10000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-7000</v>
       </c>
-      <c r="J101" s="3" t="s">
+      <c r="K101" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-13000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-6000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-50000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-24000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-13000</v>
-      </c>
-      <c r="P101" s="3">
-        <v>-6000</v>
       </c>
       <c r="Q101" s="3">
         <v>-6000</v>
       </c>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3">
+        <v>-6000</v>
+      </c>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
+        <v>-290000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-150000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-67000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>593000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-37000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-16000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-2728000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>2203000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>30000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>40000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-9000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>81000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-28000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-57000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>114000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/VYX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VYX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="92">
   <si>
     <t>VYX</t>
   </si>
@@ -656,251 +656,263 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:S102"/>
+  <dimension ref="A5:T102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>720000</v>
+      </c>
+      <c r="E8" s="3">
         <v>684000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>666000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>617000</v>
       </c>
-      <c r="G8" s="3">
-        <v>682000</v>
-      </c>
       <c r="H8" s="3">
+        <v>678000</v>
+      </c>
+      <c r="I8" s="3">
         <v>708000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>722000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>710000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>796000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>809000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>667000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>906000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3793000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1972000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1997000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1866000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2034000</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>540000</v>
+      </c>
+      <c r="E9" s="3">
         <v>512000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>509000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>480000</v>
       </c>
-      <c r="G9" s="3">
-        <v>518000</v>
-      </c>
       <c r="H9" s="3">
+        <v>522000</v>
+      </c>
+      <c r="I9" s="3">
         <v>541000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>577000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>564000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>642000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>611000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>523000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>682000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2815000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1481000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1526000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1455000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1531000</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>180000</v>
+      </c>
+      <c r="E10" s="3">
         <v>172000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>157000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>137000</v>
       </c>
-      <c r="G10" s="3">
-        <v>164000</v>
-      </c>
       <c r="H10" s="3">
+        <v>156000</v>
+      </c>
+      <c r="I10" s="3">
         <v>167000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>145000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>146000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>154000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>198000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>144000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>224000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>978000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>491000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>471000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>411000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>503000</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -920,61 +932,65 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T11" s="3"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>43000</v>
+      </c>
+      <c r="E12" s="3">
         <v>37000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>30000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>37000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>29000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>34000</v>
-      </c>
-      <c r="I12" s="3">
-        <v>41000</v>
       </c>
       <c r="J12" s="3">
         <v>41000</v>
       </c>
       <c r="K12" s="3">
+        <v>41000</v>
+      </c>
+      <c r="L12" s="3">
         <v>30000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>29000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>20000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>49000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>127000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>39000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>51000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>64000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>63000</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1026,114 +1042,123 @@
       <c r="S13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E14" s="3">
         <v>44000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>20000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>32000</v>
       </c>
-      <c r="G14" s="3">
-        <v>28000</v>
-      </c>
       <c r="H14" s="3">
+        <v>15000</v>
+      </c>
+      <c r="I14" s="3">
         <v>2000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>45000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>43000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>121000</v>
-      </c>
-      <c r="L14" s="3">
-        <v>28000</v>
       </c>
       <c r="M14" s="3">
         <v>28000</v>
       </c>
       <c r="N14" s="3">
+        <v>28000</v>
+      </c>
+      <c r="O14" s="3">
         <v>7000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>62000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>9000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>35000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>31000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>23000</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>24000</v>
+      </c>
+      <c r="E15" s="3">
         <v>55000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>58000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>60000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>39500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>70000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>86000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>81000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>105800</v>
-      </c>
-      <c r="L15" s="3">
-        <v>155000</v>
       </c>
       <c r="M15" s="3">
         <v>155000</v>
       </c>
       <c r="N15" s="3">
+        <v>155000</v>
+      </c>
+      <c r="O15" s="3">
         <v>151000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>30000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>17000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>18000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>22000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>23000</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1150,114 +1175,121 @@
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
-    </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>703000</v>
+      </c>
+      <c r="E17" s="3">
         <v>626000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>633000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>606000</v>
       </c>
-      <c r="G17" s="3">
-        <v>640000</v>
-      </c>
       <c r="H17" s="3">
+        <v>652000</v>
+      </c>
+      <c r="I17" s="3">
         <v>683000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>712000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>702000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>888000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>758000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>651000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>880000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3657000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1785000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1894000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1833000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1911000</v>
       </c>
     </row>
-    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>17000</v>
+      </c>
+      <c r="E18" s="3">
         <v>58000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>33000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>11000</v>
       </c>
-      <c r="G18" s="3">
-        <v>42000</v>
-      </c>
       <c r="H18" s="3">
+        <v>26000</v>
+      </c>
+      <c r="I18" s="3">
         <v>25000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>10000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>8000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-92000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>51000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>16000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>26000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>136000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>187000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>103000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>33000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>123000</v>
       </c>
     </row>
-    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1277,273 +1309,289 @@
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
-    </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-21000</v>
+      </c>
+      <c r="E20" s="3">
         <v>22000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>3000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-3000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>12000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>15000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>5000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>4000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>39000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>24000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>11000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>6000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>99000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>1000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>9000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>113000</v>
       </c>
     </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>62000</v>
+      </c>
+      <c r="E21" s="3">
         <v>91000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>88000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>74000</v>
       </c>
-      <c r="G21" s="3">
-        <v>69500</v>
-      </c>
       <c r="H21" s="3">
+        <v>53500</v>
+      </c>
+      <c r="I21" s="3">
         <v>80000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>91000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>85000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-25300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>182000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>160000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>171000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>845000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>338000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>256000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>189000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>389000</v>
       </c>
     </row>
-    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>16000</v>
+      </c>
+      <c r="E22" s="3">
         <v>15000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>14000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>15000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>14000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>40000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>41000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>39000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>37000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>83000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>91000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>83000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>366000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>74000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>67000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>63000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>64000</v>
       </c>
     </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>22000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-23000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-3000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-27000</v>
       </c>
-      <c r="G23" s="3">
-        <v>-8000</v>
-      </c>
       <c r="H23" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="I23" s="3">
         <v>-30000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-80000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-76000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-288000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-79000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-111000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-67000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-131000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>112000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>37000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-21000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>172000</v>
       </c>
     </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>-56000</v>
+      </c>
+      <c r="E24" s="3">
         <v>-6000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-4000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-7000</v>
       </c>
-      <c r="G24" s="3">
-        <v>1000</v>
-      </c>
       <c r="H24" s="3">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3">
         <v>-1000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>10000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-5000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-16000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>187000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>8000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>5000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>72000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>43000</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
-      </c>
       <c r="R24" s="3">
+        <v>0</v>
+      </c>
+      <c r="S24" s="3">
         <v>13000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>109000</v>
       </c>
     </row>
-    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1595,114 +1643,123 @@
       <c r="S25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>78000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-17000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-20000</v>
       </c>
-      <c r="G26" s="3">
-        <v>-9000</v>
-      </c>
       <c r="H26" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="I26" s="3">
         <v>-29000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-90000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-71000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-272000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-266000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-119000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-72000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-203000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>69000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>37000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-34000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>63000</v>
       </c>
     </row>
-    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>89000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-22000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-4000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-21000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-14000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1078000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-77000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-44000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-322000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-133000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>13000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>3000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-217000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>65000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>31000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-37000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>60000</v>
       </c>
     </row>
-    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -1754,61 +1811,67 @@
       <c r="S28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D29" s="3">
+        <v>20000</v>
+      </c>
+      <c r="E29" s="3">
         <v>-2000</v>
       </c>
-      <c r="E29" s="3">
+      <c r="F29" s="3">
         <v>-1000</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>3000</v>
       </c>
-      <c r="G29" s="3">
-        <v>-2000</v>
-      </c>
       <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
         <v>1111000</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>17000</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>31000</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>-47000</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>138000</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>136000</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>79000</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>263000</v>
       </c>
-      <c r="P29" s="3">
-        <v>0</v>
-      </c>
       <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3">
         <v>6000</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>-1000</v>
       </c>
-      <c r="S29" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -1860,8 +1923,11 @@
       <c r="S30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -1913,114 +1979,123 @@
       <c r="S31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
+        <v>21000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-22000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-3000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>3000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-12000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-15000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-5000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-4000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-39000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-24000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-11000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-6000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-99000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>1000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-1000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-9000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-113000</v>
       </c>
     </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
+        <v>98000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-19000</v>
       </c>
-      <c r="E33" s="3">
-        <v>0</v>
-      </c>
       <c r="F33" s="3">
+        <v>0</v>
+      </c>
+      <c r="G33" s="3">
         <v>-17000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-11000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1082000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-73000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-40000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-318000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-129000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>17000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>7000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>46000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>65000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>37000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-38000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>60000</v>
       </c>
     </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -2072,119 +2147,128 @@
       <c r="S34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
+        <v>98000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-19000</v>
       </c>
-      <c r="E35" s="3">
-        <v>0</v>
-      </c>
       <c r="F35" s="3">
+        <v>0</v>
+      </c>
+      <c r="G35" s="3">
         <v>-17000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-11000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1082000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-73000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-40000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-318000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-129000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>17000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>7000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>46000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>65000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>37000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-38000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>60000</v>
       </c>
     </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
     </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -2204,8 +2288,9 @@
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
-    </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T39" s="3"/>
+    </row>
+    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -2225,61 +2310,65 @@
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
-    </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T40" s="3"/>
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>231000</v>
+      </c>
+      <c r="E41" s="3">
         <v>282000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>276000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>573000</v>
       </c>
-      <c r="G41" s="3">
-        <v>724000</v>
-      </c>
       <c r="H41" s="3">
+        <v>722000</v>
+      </c>
+      <c r="I41" s="3">
         <v>795000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>204000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>246000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>259000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>675000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>547000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>519000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>221000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>434000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>398000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>412000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>447000</v>
       </c>
     </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
@@ -2308,17 +2397,17 @@
         <v>0</v>
       </c>
       <c r="L42" s="3">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="M42" s="3">
         <v>20000</v>
       </c>
       <c r="N42" s="3">
+        <v>20000</v>
+      </c>
+      <c r="O42" s="3">
         <v>33000</v>
       </c>
-      <c r="O42" s="3">
-        <v>0</v>
-      </c>
       <c r="P42" s="3">
         <v>0</v>
       </c>
@@ -2331,114 +2420,123 @@
       <c r="S42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
+        <v>470000</v>
+      </c>
+      <c r="E43" s="3">
         <v>548000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>507000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>567000</v>
       </c>
-      <c r="G43" s="3">
-        <v>539000</v>
-      </c>
       <c r="H43" s="3">
+        <v>532000</v>
+      </c>
+      <c r="I43" s="3">
         <v>623000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>429000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>484000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>414000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>950000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>986000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1009000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>550000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1116000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1085000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1071000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>959000</v>
       </c>
     </row>
-    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
+        <v>217000</v>
+      </c>
+      <c r="E44" s="3">
         <v>221000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>212000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>218000</v>
-      </c>
-      <c r="G44" s="3">
-        <v>208000</v>
       </c>
       <c r="H44" s="3">
         <v>208000</v>
       </c>
       <c r="I44" s="3">
+        <v>208000</v>
+      </c>
+      <c r="J44" s="3">
         <v>220000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>259000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>250000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>725000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>709000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>792000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>357000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>827000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>858000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>805000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>754000</v>
       </c>
     </row>
-    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
@@ -2454,97 +2552,103 @@
       <c r="G45" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="H45" s="3" t="s">
+      <c r="H45" s="3">
+        <v>12000</v>
+      </c>
+      <c r="I45" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>5000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>89000</v>
-      </c>
-      <c r="L45" s="3">
-        <v>1000</v>
       </c>
       <c r="M45" s="3">
         <v>1000</v>
       </c>
       <c r="N45" s="3">
+        <v>1000</v>
+      </c>
+      <c r="O45" s="3">
         <v>460000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1954000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>814000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>713000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>688000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>716000</v>
       </c>
     </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
+        <v>1103000</v>
+      </c>
+      <c r="E46" s="3">
         <v>1263000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1222000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1569000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1671000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1825000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1064000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1238000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1206000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>3093000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2954000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>3070000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>3082000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>3191000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>3054000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>2976000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>2876000</v>
       </c>
     </row>
-    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
@@ -2572,18 +2676,18 @@
       <c r="K47" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="L47" s="3">
-        <v>2000</v>
+      <c r="L47" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="M47" s="3">
         <v>2000</v>
       </c>
       <c r="N47" s="3">
+        <v>2000</v>
+      </c>
+      <c r="O47" s="3">
         <v>11000</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
-      </c>
       <c r="P47" s="3">
         <v>0</v>
       </c>
@@ -2596,114 +2700,123 @@
       <c r="S47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
+        <v>382000</v>
+      </c>
+      <c r="E48" s="3">
         <v>381000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>398000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>409000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>421000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>429000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>438000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>448000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>438000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1029000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1030000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1034000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>499000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>997000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1039000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1075000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1122000</v>
       </c>
     </row>
-    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
+        <v>1905000</v>
+      </c>
+      <c r="E49" s="3">
         <v>1910000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1902000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1900000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1912000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1934000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2785000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2803000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1959000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>6119000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>6181000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>5647000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>2480000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>5756000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>5825000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>5879000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>5835000</v>
       </c>
     </row>
-    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -2755,8 +2868,11 @@
       <c r="S50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -2808,61 +2924,67 @@
       <c r="S51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
+        <v>346000</v>
+      </c>
+      <c r="E52" s="3">
         <v>266000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>270000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>262000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>259000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>261000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>252000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>283000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1148000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2550000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>523000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1085000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>6342000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1839000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1838000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1785000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1808000</v>
       </c>
     </row>
-    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -2914,61 +3036,67 @@
       <c r="S53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
+        <v>3921000</v>
+      </c>
+      <c r="E54" s="3">
         <v>4003000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3984000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>4336000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>4452000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>4674000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>4783000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>5007000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>4990000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>13223000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>11279000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>11442000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>11507000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>11783000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>11756000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>11715000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>11641000</v>
       </c>
     </row>
-    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -2988,8 +3116,9 @@
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
-    </row>
-    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T55" s="3"/>
+    </row>
+    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -3009,66 +3138,70 @@
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
-    </row>
-    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T56" s="3"/>
+    </row>
+    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
+        <v>346000</v>
+      </c>
+      <c r="E57" s="3">
         <v>375000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>340000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>325000</v>
       </c>
-      <c r="G57" s="3">
-        <v>332000</v>
-      </c>
       <c r="H57" s="3">
+        <v>324000</v>
+      </c>
+      <c r="I57" s="3">
         <v>400000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>478000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>482000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>440000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>820000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>832000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>952000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>594000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>876000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>949000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>901000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>826000</v>
       </c>
     </row>
-    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>52000</v>
       </c>
       <c r="E58" s="3">
         <v>0</v>
@@ -3077,152 +3210,161 @@
         <v>0</v>
       </c>
       <c r="G58" s="3">
+        <v>0</v>
+      </c>
+      <c r="H58" s="3">
         <v>51000</v>
       </c>
-      <c r="H58" s="3">
-        <v>0</v>
-      </c>
       <c r="I58" s="3">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="J58" s="3">
         <v>15000</v>
       </c>
       <c r="K58" s="3">
+        <v>15000</v>
+      </c>
+      <c r="L58" s="3">
         <v>63000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>113000</v>
-      </c>
-      <c r="M58" s="3">
-        <v>105000</v>
       </c>
       <c r="N58" s="3">
         <v>105000</v>
       </c>
       <c r="O58" s="3">
+        <v>105000</v>
+      </c>
+      <c r="P58" s="3">
         <v>110000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>106000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>108000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>83000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>73000</v>
       </c>
     </row>
-    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
+        <v>569000</v>
+      </c>
+      <c r="E59" s="3">
         <v>639000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>619000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>988000</v>
       </c>
-      <c r="G59" s="3">
-        <v>933000</v>
-      </c>
       <c r="H59" s="3">
+        <v>941000</v>
+      </c>
+      <c r="I59" s="3">
         <v>1008000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>668000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>738000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>704000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1429000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1512000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1536000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2682000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1788000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1776000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1846000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1909000</v>
       </c>
     </row>
-    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
+        <v>1065000</v>
+      </c>
+      <c r="E60" s="3">
         <v>1113000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1054000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1406000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1420000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1527000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1254000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1335000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1333000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2680000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2657000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2816000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2713000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2770000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2833000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>2830000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>2808000</v>
       </c>
     </row>
-    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
@@ -3230,105 +3372,111 @@
         <v>1331000</v>
       </c>
       <c r="E61" s="3">
+        <v>1331000</v>
+      </c>
+      <c r="F61" s="3">
         <v>1337000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1340000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1349000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1351000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2847000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2917000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2821000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>7743000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>5660000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>5746000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>5555000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>5611000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>5497000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>5516000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>5518000</v>
       </c>
     </row>
-    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
+        <v>190000</v>
+      </c>
+      <c r="E62" s="3">
         <v>214000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>231000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>253000</v>
       </c>
-      <c r="G62" s="3">
-        <v>278000</v>
-      </c>
       <c r="H62" s="3">
+        <v>280000</v>
+      </c>
+      <c r="I62" s="3">
         <v>293000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>276000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>292000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>320000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>360000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>373000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>364000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1485000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1681000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1778000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1770000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1782000</v>
       </c>
     </row>
-    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -3380,8 +3528,11 @@
       <c r="S63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -3433,8 +3584,11 @@
       <c r="S64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -3486,61 +3640,67 @@
       <c r="S65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
+        <v>2766000</v>
+      </c>
+      <c r="E66" s="3">
         <v>2879000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2841000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3203000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3245000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3387000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>4594000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>4767000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>4689000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>11576000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>9450000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>9679000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>9752000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>10063000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>10111000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>10118000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>10111000</v>
       </c>
     </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -3560,8 +3720,9 @@
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
-    </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T67" s="3"/>
+    </row>
+    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -3613,8 +3774,11 @@
       <c r="S68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -3666,13 +3830,16 @@
       <c r="S69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
       <c r="D70" s="3">
-        <v>276000</v>
+        <v>207000</v>
       </c>
       <c r="E70" s="3">
         <v>276000</v>
@@ -3696,7 +3863,7 @@
         <v>276000</v>
       </c>
       <c r="L70" s="3">
-        <v>275000</v>
+        <v>276000</v>
       </c>
       <c r="M70" s="3">
         <v>275000</v>
@@ -3714,13 +3881,16 @@
         <v>275000</v>
       </c>
       <c r="R70" s="3">
-        <v>274000</v>
+        <v>275000</v>
       </c>
       <c r="S70" s="3">
         <v>274000</v>
       </c>
-    </row>
-    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T70" s="3">
+        <v>274000</v>
+      </c>
+    </row>
+    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -3772,61 +3942,67 @@
       <c r="S71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
+        <v>559000</v>
+      </c>
+      <c r="E72" s="3">
         <v>470000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>492000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>496000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>535000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>561000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-517000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-463000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-421000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>967000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1095000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1080000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1075000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>1095000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>1030000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>993000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>1031000</v>
       </c>
     </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -3878,8 +4054,11 @@
       <c r="S73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -3931,8 +4110,11 @@
       <c r="S74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -3984,61 +4166,67 @@
       <c r="S75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
+        <v>948000</v>
+      </c>
+      <c r="E76" s="3">
         <v>848000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>867000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>857000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>933000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1013000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-85000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-34000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>25000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1372000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1555000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1489000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1480000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1445000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1370000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1323000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1256000</v>
       </c>
     </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -4090,119 +4278,128 @@
       <c r="S77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
     </row>
-    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
+        <v>98000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-19000</v>
       </c>
-      <c r="E81" s="3">
-        <v>0</v>
-      </c>
       <c r="F81" s="3">
+        <v>0</v>
+      </c>
+      <c r="G81" s="3">
         <v>-17000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-11000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1082000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-73000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-40000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-318000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-129000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>17000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>7000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>46000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>65000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>37000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-38000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>60000</v>
       </c>
     </row>
-    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -4222,61 +4419,65 @@
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
-    </row>
-    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T82" s="3"/>
+    </row>
+    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D83" s="3">
+        <v>-79000</v>
+      </c>
+      <c r="E83" s="3">
         <v>63000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>78000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>74000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>-38000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>155000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>137000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>134000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>-10000</v>
       </c>
-      <c r="L83" s="3" t="s">
+      <c r="M83" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>107000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>106000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>610000</v>
-      </c>
-      <c r="P83" s="3">
-        <v>152000</v>
       </c>
       <c r="Q83" s="3">
         <v>152000</v>
       </c>
       <c r="R83" s="3">
+        <v>152000</v>
+      </c>
+      <c r="S83" s="3">
         <v>147000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>153000</v>
       </c>
     </row>
-    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -4328,8 +4529,11 @@
       <c r="S84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -4381,8 +4585,11 @@
       <c r="S85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -4434,8 +4641,11 @@
       <c r="S86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -4487,8 +4697,11 @@
       <c r="S87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -4540,61 +4753,67 @@
       <c r="S88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
+        <v>60000</v>
+      </c>
+      <c r="E89" s="3">
         <v>14000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-242000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-42000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-170000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>11000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>62000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-35000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-33000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>189000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>227000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>311000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>427000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>126000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>84000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>34000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>252000</v>
       </c>
     </row>
-    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -4614,61 +4833,65 @@
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
-    </row>
-    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T90" s="3"/>
+    </row>
+    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D91" s="3">
+        <v>-146000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-4000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-7000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-8000</v>
       </c>
-      <c r="G91" s="3">
-        <v>-7000</v>
-      </c>
       <c r="H91" s="3">
+        <v>-194000</v>
+      </c>
+      <c r="I91" s="3">
         <v>-2000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-13000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-8000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-18000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-42000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-51000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-19000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-88000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-115000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-94000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-80000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-106000</v>
       </c>
     </row>
-    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -4720,8 +4943,11 @@
       <c r="S92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -4773,61 +4999,67 @@
       <c r="S93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
+        <v>-24000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-35000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-40000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-35000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>172000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>2098000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-27000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-54000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>15000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-111000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-108000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-86000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-387000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-121000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-91000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-86000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-114000</v>
       </c>
     </row>
-    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -4847,8 +5079,9 @@
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
-    </row>
-    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T95" s="3"/>
+    </row>
+    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
@@ -4885,8 +5118,8 @@
       <c r="N96" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -4900,8 +5133,11 @@
       <c r="S96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -4953,8 +5189,11 @@
       <c r="S97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -5006,8 +5245,11 @@
       <c r="S98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -5059,61 +5301,67 @@
       <c r="S99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D100" s="3">
+        <v>-85000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-4000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-12000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-74000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-64000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1511000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-65000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>80000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-2718000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>2145000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-91000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-175000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>1000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>100000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-8000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>1000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-18000</v>
       </c>
     </row>
-    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
@@ -5121,101 +5369,107 @@
         <v>-5000</v>
       </c>
       <c r="E101" s="3">
-        <v>-7000</v>
+        <v>-5000</v>
       </c>
       <c r="F101" s="3">
         <v>-7000</v>
       </c>
       <c r="G101" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="H101" s="3">
         <v>8000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-20000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>2000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-10000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-7000</v>
       </c>
-      <c r="L101" s="3" t="s">
+      <c r="M101" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-13000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-6000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-50000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-24000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-13000</v>
-      </c>
-      <c r="R101" s="3">
-        <v>-6000</v>
       </c>
       <c r="S101" s="3">
         <v>-6000</v>
       </c>
-    </row>
-    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T101" s="3">
+        <v>-6000</v>
+      </c>
+    </row>
+    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
+        <v>-49000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-26000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-290000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-150000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-67000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>593000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-37000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-16000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-2728000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>2203000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>30000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>40000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-9000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>81000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-28000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-57000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>114000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/VYX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VYX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="92">
   <si>
     <t>VYX</t>
   </si>
@@ -656,263 +656,276 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>606000</v>
+      </c>
+      <c r="E8" s="3">
         <v>720000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>684000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>666000</v>
       </c>
-      <c r="G8" s="3">
-        <v>617000</v>
-      </c>
       <c r="H8" s="3">
+        <v>612000</v>
+      </c>
+      <c r="I8" s="3">
         <v>678000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>708000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>722000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>710000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>796000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>809000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>667000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>906000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3793000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1972000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1997000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1866000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2034000</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>476000</v>
+      </c>
+      <c r="E9" s="3">
         <v>540000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>512000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>509000</v>
       </c>
-      <c r="G9" s="3">
-        <v>480000</v>
-      </c>
       <c r="H9" s="3">
+        <v>478000</v>
+      </c>
+      <c r="I9" s="3">
         <v>522000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>541000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>577000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>564000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>642000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>611000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>523000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>682000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2815000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1481000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1526000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1455000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1531000</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>130000</v>
+      </c>
+      <c r="E10" s="3">
         <v>180000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>172000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>157000</v>
       </c>
-      <c r="G10" s="3">
-        <v>137000</v>
-      </c>
       <c r="H10" s="3">
+        <v>134000</v>
+      </c>
+      <c r="I10" s="3">
         <v>156000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>167000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>145000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>146000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>154000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>198000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>144000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>224000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>978000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>491000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>471000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>411000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>503000</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -933,64 +946,68 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>39000</v>
+      </c>
+      <c r="E12" s="3">
         <v>43000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>37000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>30000</v>
       </c>
-      <c r="G12" s="3">
-        <v>37000</v>
-      </c>
       <c r="H12" s="3">
+        <v>40000</v>
+      </c>
+      <c r="I12" s="3">
         <v>29000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>34000</v>
-      </c>
-      <c r="J12" s="3">
-        <v>41000</v>
       </c>
       <c r="K12" s="3">
         <v>41000</v>
       </c>
       <c r="L12" s="3">
+        <v>41000</v>
+      </c>
+      <c r="M12" s="3">
         <v>30000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>29000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>20000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>49000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>127000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>39000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>51000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>64000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>63000</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1045,120 +1062,129 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F14" s="3">
         <v>44000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>20000</v>
       </c>
-      <c r="G14" s="3">
-        <v>32000</v>
-      </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="I14" s="3">
         <v>15000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>2000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>45000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>43000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>121000</v>
-      </c>
-      <c r="M14" s="3">
-        <v>28000</v>
       </c>
       <c r="N14" s="3">
         <v>28000</v>
       </c>
       <c r="O14" s="3">
+        <v>28000</v>
+      </c>
+      <c r="P14" s="3">
         <v>7000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>62000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>9000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>35000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>31000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>23000</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>53000</v>
+      </c>
+      <c r="E15" s="3">
         <v>24000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>55000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>58000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>60000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>39500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>70000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>86000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>81000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>105800</v>
-      </c>
-      <c r="M15" s="3">
-        <v>155000</v>
       </c>
       <c r="N15" s="3">
         <v>155000</v>
       </c>
       <c r="O15" s="3">
+        <v>155000</v>
+      </c>
+      <c r="P15" s="3">
         <v>151000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>30000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>17000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>18000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>22000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>23000</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1176,120 +1202,127 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>626000</v>
+      </c>
+      <c r="E17" s="3">
         <v>703000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>626000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>633000</v>
       </c>
-      <c r="G17" s="3">
-        <v>606000</v>
-      </c>
       <c r="H17" s="3">
+        <v>634000</v>
+      </c>
+      <c r="I17" s="3">
         <v>652000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>683000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>712000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>702000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>888000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>758000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>651000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>880000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3657000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1785000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1894000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1833000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1911000</v>
       </c>
     </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>-20000</v>
+      </c>
+      <c r="E18" s="3">
         <v>17000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>58000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>33000</v>
       </c>
-      <c r="G18" s="3">
-        <v>11000</v>
-      </c>
       <c r="H18" s="3">
+        <v>-22000</v>
+      </c>
+      <c r="I18" s="3">
         <v>26000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>25000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>10000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>8000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-92000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>51000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>16000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>26000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>136000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>187000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>103000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>33000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>123000</v>
       </c>
     </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1310,288 +1343,304 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-21000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>22000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>3000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-3000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>12000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>15000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>5000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>4000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>39000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>24000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>11000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>6000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>99000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-1000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>1000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>9000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>113000</v>
       </c>
     </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>27000</v>
+      </c>
+      <c r="E21" s="3">
         <v>62000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>91000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>88000</v>
       </c>
-      <c r="G21" s="3">
-        <v>74000</v>
-      </c>
       <c r="H21" s="3">
+        <v>41000</v>
+      </c>
+      <c r="I21" s="3">
         <v>53500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>80000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>91000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>85000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-25300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>182000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>160000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>171000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>845000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>338000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>256000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>189000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>389000</v>
       </c>
     </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>15000</v>
+      </c>
+      <c r="E22" s="3">
         <v>16000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>15000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>14000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>15000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>14000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>40000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>41000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>39000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>37000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>83000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>91000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>83000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>366000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>74000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>67000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>63000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>64000</v>
       </c>
     </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>-41000</v>
+      </c>
+      <c r="E23" s="3">
         <v>22000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-23000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-3000</v>
       </c>
-      <c r="G23" s="3">
-        <v>-27000</v>
-      </c>
       <c r="H23" s="3">
+        <v>-28000</v>
+      </c>
+      <c r="I23" s="3">
         <v>-11000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-30000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-80000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-76000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-288000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-79000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-111000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-67000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-131000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>112000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>37000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-21000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>172000</v>
       </c>
     </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>-39000</v>
+      </c>
+      <c r="E24" s="3">
         <v>-56000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-6000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-4000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-7000</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
       <c r="I24" s="3">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3">
         <v>-1000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>10000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-5000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-16000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>187000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>8000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>5000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>72000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>43000</v>
       </c>
-      <c r="R24" s="3">
-        <v>0</v>
-      </c>
       <c r="S24" s="3">
+        <v>0</v>
+      </c>
+      <c r="T24" s="3">
         <v>13000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>109000</v>
       </c>
     </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1646,120 +1695,129 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E26" s="3">
         <v>78000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-17000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1000</v>
       </c>
-      <c r="G26" s="3">
-        <v>-20000</v>
-      </c>
       <c r="H26" s="3">
+        <v>-21000</v>
+      </c>
+      <c r="I26" s="3">
         <v>-11000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-29000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-90000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-71000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-272000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-266000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-119000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-72000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-203000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>69000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>37000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-34000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>63000</v>
       </c>
     </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="E27" s="3">
         <v>89000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-22000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-4000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-21000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-14000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1078000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-77000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-44000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-322000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-133000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>13000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>3000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-217000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>65000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>31000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-37000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>60000</v>
       </c>
     </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -1814,64 +1872,70 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D29" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E29" s="3">
         <v>20000</v>
       </c>
-      <c r="E29" s="3">
+      <c r="F29" s="3">
         <v>-2000</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>-1000</v>
       </c>
-      <c r="G29" s="3">
-        <v>3000</v>
-      </c>
       <c r="H29" s="3">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
         <v>1111000</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>17000</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>31000</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>-47000</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>138000</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>136000</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>79000</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>263000</v>
       </c>
-      <c r="Q29" s="3">
-        <v>0</v>
-      </c>
       <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3">
         <v>6000</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>-1000</v>
       </c>
-      <c r="T29" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -1926,8 +1990,11 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -1982,120 +2049,129 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="E32" s="3">
         <v>21000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-22000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-3000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>3000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-12000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-15000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-5000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-4000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-39000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-24000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-11000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-6000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-99000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>1000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-1000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-9000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-113000</v>
       </c>
     </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="E33" s="3">
         <v>98000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-19000</v>
       </c>
-      <c r="F33" s="3">
-        <v>0</v>
-      </c>
       <c r="G33" s="3">
+        <v>0</v>
+      </c>
+      <c r="H33" s="3">
         <v>-17000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-11000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1082000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-73000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-40000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-318000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-129000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>17000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>7000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>46000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>65000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>37000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-38000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>60000</v>
       </c>
     </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -2150,125 +2226,134 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="E35" s="3">
         <v>98000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-19000</v>
       </c>
-      <c r="F35" s="3">
-        <v>0</v>
-      </c>
       <c r="G35" s="3">
+        <v>0</v>
+      </c>
+      <c r="H35" s="3">
         <v>-17000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-11000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1082000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-73000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-40000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-318000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-129000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>17000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>7000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>46000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>65000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>37000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-38000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>60000</v>
       </c>
     </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
     </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -2289,8 +2374,9 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -2311,64 +2397,68 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>232000</v>
+      </c>
+      <c r="E41" s="3">
         <v>231000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>282000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>276000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>573000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>722000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>795000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>204000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>246000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>259000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>675000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>547000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>519000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>221000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>434000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>398000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>412000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>447000</v>
       </c>
     </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
@@ -2400,17 +2490,17 @@
         <v>0</v>
       </c>
       <c r="M42" s="3">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="N42" s="3">
         <v>20000</v>
       </c>
       <c r="O42" s="3">
+        <v>20000</v>
+      </c>
+      <c r="P42" s="3">
         <v>33000</v>
       </c>
-      <c r="P42" s="3">
-        <v>0</v>
-      </c>
       <c r="Q42" s="3">
         <v>0</v>
       </c>
@@ -2423,125 +2513,134 @@
       <c r="T42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
+        <v>457000</v>
+      </c>
+      <c r="E43" s="3">
         <v>470000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>548000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>507000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>567000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>532000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>623000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>429000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>484000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>414000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>950000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>986000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1009000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>550000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1116000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1085000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1071000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>959000</v>
       </c>
     </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
+        <v>159000</v>
+      </c>
+      <c r="E44" s="3">
         <v>217000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>221000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>212000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>218000</v>
-      </c>
-      <c r="H44" s="3">
-        <v>208000</v>
       </c>
       <c r="I44" s="3">
         <v>208000</v>
       </c>
       <c r="J44" s="3">
+        <v>208000</v>
+      </c>
+      <c r="K44" s="3">
         <v>220000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>259000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>250000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>725000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>709000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>792000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>357000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>827000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>858000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>805000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>754000</v>
       </c>
     </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>91</v>
+      <c r="D45" s="3">
+        <v>1000</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>91</v>
@@ -2552,103 +2651,109 @@
       <c r="G45" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="H45" s="3">
+      <c r="H45" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="I45" s="3">
         <v>12000</v>
       </c>
-      <c r="I45" s="3" t="s">
+      <c r="J45" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>5000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>89000</v>
-      </c>
-      <c r="M45" s="3">
-        <v>1000</v>
       </c>
       <c r="N45" s="3">
         <v>1000</v>
       </c>
       <c r="O45" s="3">
+        <v>1000</v>
+      </c>
+      <c r="P45" s="3">
         <v>460000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1954000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>814000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>713000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>688000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>716000</v>
       </c>
     </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
+        <v>1174000</v>
+      </c>
+      <c r="E46" s="3">
         <v>1103000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1263000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1222000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1569000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1671000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1825000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1064000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1238000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1206000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>3093000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2954000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>3070000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>3082000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>3191000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>3054000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>2976000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>2876000</v>
       </c>
     </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
@@ -2679,18 +2784,18 @@
       <c r="L47" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="M47" s="3">
-        <v>2000</v>
+      <c r="M47" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="N47" s="3">
         <v>2000</v>
       </c>
       <c r="O47" s="3">
+        <v>2000</v>
+      </c>
+      <c r="P47" s="3">
         <v>11000</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
-      </c>
       <c r="Q47" s="3">
         <v>0</v>
       </c>
@@ -2703,120 +2808,129 @@
       <c r="T47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
+        <v>375000</v>
+      </c>
+      <c r="E48" s="3">
         <v>382000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>381000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>398000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>409000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>421000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>429000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>438000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>448000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>438000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1029000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1030000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1034000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>499000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>997000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1039000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1075000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1122000</v>
       </c>
     </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
+        <v>1901000</v>
+      </c>
+      <c r="E49" s="3">
         <v>1905000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1910000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1902000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1900000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1912000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1934000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2785000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2803000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1959000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>6119000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>6181000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>5647000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>2480000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>5756000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>5825000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>5879000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>5835000</v>
       </c>
     </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -2871,8 +2985,11 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -2927,64 +3044,70 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
+        <v>278000</v>
+      </c>
+      <c r="E52" s="3">
         <v>346000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>266000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>270000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>262000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>259000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>261000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>252000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>283000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1148000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2550000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>523000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1085000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>6342000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1839000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1838000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1785000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1808000</v>
       </c>
     </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -3039,64 +3162,70 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
+        <v>3923000</v>
+      </c>
+      <c r="E54" s="3">
         <v>3921000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>4003000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3984000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>4336000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>4452000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>4674000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>4783000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>5007000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>4990000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>13223000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>11279000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>11442000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>11507000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>11783000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>11756000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>11715000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>11641000</v>
       </c>
     </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -3117,8 +3246,9 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -3139,73 +3269,77 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
+        <v>371000</v>
+      </c>
+      <c r="E57" s="3">
         <v>346000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>375000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>340000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>325000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>324000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>400000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>478000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>482000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>440000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>820000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>832000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>952000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>594000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>876000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>949000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>901000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>826000</v>
       </c>
     </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
+        <v>0</v>
+      </c>
+      <c r="E58" s="3">
         <v>52000</v>
       </c>
-      <c r="E58" s="3">
-        <v>0</v>
-      </c>
       <c r="F58" s="3">
         <v>0</v>
       </c>
@@ -3213,270 +3347,285 @@
         <v>0</v>
       </c>
       <c r="H58" s="3">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3">
         <v>51000</v>
       </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
       <c r="J58" s="3">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="K58" s="3">
         <v>15000</v>
       </c>
       <c r="L58" s="3">
+        <v>15000</v>
+      </c>
+      <c r="M58" s="3">
         <v>63000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>113000</v>
-      </c>
-      <c r="N58" s="3">
-        <v>105000</v>
       </c>
       <c r="O58" s="3">
         <v>105000</v>
       </c>
       <c r="P58" s="3">
+        <v>105000</v>
+      </c>
+      <c r="Q58" s="3">
         <v>110000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>106000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>108000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>83000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>73000</v>
       </c>
     </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
+        <v>644000</v>
+      </c>
+      <c r="E59" s="3">
         <v>569000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>639000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>619000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>988000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>941000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1008000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>668000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>738000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>704000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1429000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1512000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1536000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2682000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1788000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1776000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1846000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1909000</v>
       </c>
     </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
+        <v>1110000</v>
+      </c>
+      <c r="E60" s="3">
         <v>1065000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1113000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1054000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1406000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1420000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1527000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1254000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1335000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1333000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2680000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2657000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2816000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2713000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2770000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>2833000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>2830000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>2808000</v>
       </c>
     </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
-        <v>1331000</v>
+        <v>1319000</v>
       </c>
       <c r="E61" s="3">
         <v>1331000</v>
       </c>
       <c r="F61" s="3">
+        <v>1331000</v>
+      </c>
+      <c r="G61" s="3">
         <v>1337000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1340000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1349000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1351000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2847000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2917000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2821000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>7743000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>5660000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>5746000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>5555000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>5611000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>5497000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>5516000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>5518000</v>
       </c>
     </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
+        <v>181000</v>
+      </c>
+      <c r="E62" s="3">
         <v>190000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>214000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>231000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>253000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>280000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>293000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>276000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>292000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>320000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>360000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>373000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>364000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1485000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1681000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1778000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1770000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1782000</v>
       </c>
     </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -3531,8 +3680,11 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -3587,8 +3739,11 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -3643,64 +3798,70 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
+        <v>2788000</v>
+      </c>
+      <c r="E66" s="3">
         <v>2766000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2879000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2841000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3203000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3245000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3387000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>4594000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>4767000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>4689000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>11576000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>9450000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>9679000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>9752000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>10063000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>10111000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>10118000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>10111000</v>
       </c>
     </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -3721,8 +3882,9 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -3777,8 +3939,11 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -3833,8 +3998,11 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -3842,7 +4010,7 @@
         <v>207000</v>
       </c>
       <c r="E70" s="3">
-        <v>276000</v>
+        <v>207000</v>
       </c>
       <c r="F70" s="3">
         <v>276000</v>
@@ -3866,7 +4034,7 @@
         <v>276000</v>
       </c>
       <c r="M70" s="3">
-        <v>275000</v>
+        <v>276000</v>
       </c>
       <c r="N70" s="3">
         <v>275000</v>
@@ -3884,13 +4052,16 @@
         <v>275000</v>
       </c>
       <c r="S70" s="3">
-        <v>274000</v>
+        <v>275000</v>
       </c>
       <c r="T70" s="3">
         <v>274000</v>
       </c>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U70" s="3">
+        <v>274000</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -3945,64 +4116,70 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
+        <v>551000</v>
+      </c>
+      <c r="E72" s="3">
         <v>559000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>470000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>492000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>496000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>535000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>561000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-517000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-463000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-421000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>967000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1095000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1080000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>1075000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>1095000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>1030000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>993000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>1031000</v>
       </c>
     </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -4057,8 +4234,11 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -4113,8 +4293,11 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -4169,64 +4352,70 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
+        <v>928000</v>
+      </c>
+      <c r="E76" s="3">
         <v>948000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>848000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>867000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>857000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>933000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1013000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-85000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-34000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>25000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1372000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1555000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1489000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1480000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1445000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1370000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1323000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1256000</v>
       </c>
     </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -4281,125 +4470,134 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
     </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="E81" s="3">
         <v>98000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-19000</v>
       </c>
-      <c r="F81" s="3">
-        <v>0</v>
-      </c>
       <c r="G81" s="3">
+        <v>0</v>
+      </c>
+      <c r="H81" s="3">
         <v>-17000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-11000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1082000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-73000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-40000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-318000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-129000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>17000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>7000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>46000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>65000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>37000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-38000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>60000</v>
       </c>
     </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -4420,64 +4618,68 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D83" s="3">
+        <v>54000</v>
+      </c>
+      <c r="E83" s="3">
         <v>-79000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>63000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>78000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>74000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>-38000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>155000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>137000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>134000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>-10000</v>
       </c>
-      <c r="M83" s="3" t="s">
+      <c r="N83" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>107000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>106000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>610000</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>152000</v>
       </c>
       <c r="R83" s="3">
         <v>152000</v>
       </c>
       <c r="S83" s="3">
+        <v>152000</v>
+      </c>
+      <c r="T83" s="3">
         <v>147000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>153000</v>
       </c>
     </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -4532,8 +4734,11 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -4588,8 +4793,11 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -4644,8 +4852,11 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -4700,8 +4911,11 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -4756,64 +4970,70 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
+        <v>42000</v>
+      </c>
+      <c r="E89" s="3">
         <v>60000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>14000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-242000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-42000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-170000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>11000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>62000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-35000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-33000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>189000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>227000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>311000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>427000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>126000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>84000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>34000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>252000</v>
       </c>
     </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -4834,64 +5054,68 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D91" s="3">
+        <v>-36000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-146000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-4000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-7000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
+        <v>-39000</v>
+      </c>
+      <c r="I91" s="3">
+        <v>-194000</v>
+      </c>
+      <c r="J91" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="K91" s="3">
+        <v>-13000</v>
+      </c>
+      <c r="L91" s="3">
         <v>-8000</v>
       </c>
-      <c r="H91" s="3">
-        <v>-194000</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-2000</v>
-      </c>
-      <c r="J91" s="3">
-        <v>-13000</v>
-      </c>
-      <c r="K91" s="3">
-        <v>-8000</v>
-      </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-18000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-42000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-51000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-19000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-88000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-115000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-94000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-80000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-106000</v>
       </c>
     </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -4946,8 +5170,11 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -5002,64 +5229,70 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
+        <v>-21000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-24000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-35000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-40000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-35000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>172000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>2098000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-27000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-54000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>15000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-111000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-108000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-86000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-387000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-121000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-91000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-86000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-114000</v>
       </c>
     </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -5080,8 +5313,9 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
@@ -5121,8 +5355,8 @@
       <c r="O96" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -5136,8 +5370,11 @@
       <c r="T96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -5192,8 +5429,11 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -5248,8 +5488,11 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -5304,172 +5547,184 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D100" s="3">
+        <v>-18000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-85000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-4000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-12000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-74000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-64000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1511000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-65000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>80000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-2718000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>2145000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-91000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-175000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>100000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-8000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>1000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-18000</v>
       </c>
     </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D101" s="3">
-        <v>-5000</v>
+        <v>1000</v>
       </c>
       <c r="E101" s="3">
         <v>-5000</v>
       </c>
       <c r="F101" s="3">
-        <v>-7000</v>
+        <v>-5000</v>
       </c>
       <c r="G101" s="3">
         <v>-7000</v>
       </c>
       <c r="H101" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="I101" s="3">
         <v>8000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-20000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>2000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-10000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-7000</v>
       </c>
-      <c r="M101" s="3" t="s">
+      <c r="N101" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-13000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-6000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-50000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-24000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-13000</v>
-      </c>
-      <c r="S101" s="3">
-        <v>-6000</v>
       </c>
       <c r="T101" s="3">
         <v>-6000</v>
       </c>
-    </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U101" s="3">
+        <v>-6000</v>
+      </c>
+    </row>
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-49000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-26000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-290000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-150000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-67000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>593000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-37000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-16000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-2728000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>2203000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>30000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>40000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-9000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>81000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-28000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-57000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>114000</v>
       </c>
     </row>
